--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>8500</v>
+        <v>8800</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>10500</v>
+        <v>11500</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>7000</v>
+        <v>7300</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>15000</v>
+        <v>15300</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>13400</v>
+        <v>14400</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>10000</v>
+        <v>10300</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>6500</v>
+        <v>6800</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>14000</v>
+        <v>14600</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>15000</v>
+        <v>15600</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>999</v>
+        <v>1999</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>7200</v>
+        <v>8200</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>9000</v>
+        <v>9300</v>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>13000</v>
+        <v>13300</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>8000</v>
+        <v>8300</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>7000</v>
+        <v>7300</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>14500</v>
+        <v>15100</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>750</v>
+        <v>1750</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>3900</v>
+        <v>4200</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>5999</v>
+        <v>6299</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4700</v>
+        <v>5000</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>5300</v>
+        <v>5600</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>5800</v>
+        <v>6100</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>2900</v>
+        <v>3200</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>7800</v>
+        <v>8100</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>4300</v>
+        <v>4600</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>2900</v>
+        <v>3200</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>5300</v>
+        <v>5600</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>4300</v>
+        <v>4600</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>9400</v>
+        <v>10400</v>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>42000</v>
+        <v>43000</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>30000</v>
+        <v>31000</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>3900</v>
+        <v>4200</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>5750</v>
+        <v>6050</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>7950</v>
+        <v>8250</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>8000</v>
+        <v>8300</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>3000</v>
+        <v>3300</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>5500</v>
+        <v>5800</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>5000</v>
+        <v>5300</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>5000</v>
+        <v>5300</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>2300</v>
+        <v>2600</v>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>5000</v>
+        <v>5300</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>6800</v>
+        <v>7100</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>3999</v>
+        <v>4999</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>9500</v>
+        <v>10500</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>4450</v>
+        <v>5450</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>4200</v>
+        <v>5200</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>3999</v>
+        <v>4999</v>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>3700</v>
+        <v>4700</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>3700</v>
+        <v>4700</v>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>3900</v>
+        <v>4900</v>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
@@ -7802,7 +7802,7 @@
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>7900</v>
+        <v>8900</v>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         </is>
       </c>
       <c r="F129" s="2" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>4200</v>
+        <v>5200</v>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="F131" s="2" t="n">
-        <v>650</v>
+        <v>1650</v>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>2600</v>
+        <v>3600</v>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>2700</v>
+        <v>3700</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="F135" s="2" t="n">
-        <v>2400</v>
+        <v>3400</v>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="F137" s="2" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>2600</v>
+        <v>3600</v>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>6500</v>
+        <v>7500</v>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>550</v>
+        <v>1550</v>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
@@ -9484,7 +9484,7 @@
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>470</v>
+        <v>1470</v>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         </is>
       </c>
       <c r="F147" s="2" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="F149" s="2" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>6200</v>
+        <v>7200</v>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>2600</v>
+        <v>3600</v>
       </c>
       <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>2200</v>
+        <v>3200</v>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>450</v>
+        <v>1450</v>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         </is>
       </c>
       <c r="F154" s="2" t="n">
-        <v>10000</v>
+        <v>10600</v>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="F155" s="2" t="n">
-        <v>9000</v>
+        <v>9600</v>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         </is>
       </c>
       <c r="F156" s="2" t="n">
-        <v>26000</v>
+        <v>26600</v>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         </is>
       </c>
       <c r="F157" s="2" t="n">
-        <v>7400</v>
+        <v>8000</v>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>12500</v>
+        <v>13100</v>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="F159" s="2" t="n">
-        <v>2700</v>
+        <v>3300</v>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         </is>
       </c>
       <c r="F160" s="2" t="n">
-        <v>6800</v>
+        <v>7400</v>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="F161" s="2" t="n">
-        <v>25000</v>
+        <v>25600</v>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>11000</v>
+        <v>11600</v>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         </is>
       </c>
       <c r="F163" s="2" t="n">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>14500</v>
+        <v>15500</v>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="F169" s="2" t="n">
-        <v>9500</v>
+        <v>10500</v>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         </is>
       </c>
       <c r="F170" s="2" t="n">
-        <v>9500</v>
+        <v>10500</v>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         </is>
       </c>
       <c r="F171" s="2" t="n">
-        <v>6500</v>
+        <v>7500</v>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="F173" s="2" t="n">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
@@ -11254,7 +11254,7 @@
         </is>
       </c>
       <c r="F174" s="2" t="n">
-        <v>4450</v>
+        <v>5450</v>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         </is>
       </c>
       <c r="F175" s="2" t="n">
-        <v>3600</v>
+        <v>4600</v>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>10500</v>
+        <v>11500</v>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         </is>
       </c>
       <c r="F177" s="2" t="n">
-        <v>4200</v>
+        <v>5200</v>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         </is>
       </c>
       <c r="F178" s="2" t="n">
-        <v>15500</v>
+        <v>16500</v>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="F179" s="2" t="n">
-        <v>3100</v>
+        <v>4100</v>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         </is>
       </c>
       <c r="F181" s="2" t="n">
-        <v>10800</v>
+        <v>11800</v>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="F182" s="2" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="G182" s="2" t="inlineStr"/>
       <c r="H182" s="2" t="inlineStr">
@@ -11832,7 +11832,7 @@
         </is>
       </c>
       <c r="F183" s="2" t="n">
-        <v>3350</v>
+        <v>4350</v>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         </is>
       </c>
       <c r="F184" s="2" t="n">
-        <v>4600</v>
+        <v>5600</v>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>

--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -6664,7 +6664,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Автокран КС-3577 (500А) Start Scale Models (SSM)</t>
+          <t>Автокран КС-3577 (500А) КАЧЕСТВО = ЦЕНА (ВЫБОРКА)</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>16000</v>
+        <v>13000</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>

--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N779"/>
+  <dimension ref="A1:N781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45927,34 +45927,34 @@
         <v>740</v>
       </c>
       <c r="B741" t="n">
-        <v>188469</v>
+        <v>159729</v>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>SMART ForTwo Cabriolet Rally A451 2014</t>
+          <t>LINCOLN TownCar Limousine 2000</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-10-at-233229-3.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-10-at-233229-6.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-10-at-233229-5.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-10-at-233229-4.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011330-1.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011330-2.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011330-3.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011333-1.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011330.jpg</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>699691</t>
+          <t>6993505</t>
         </is>
       </c>
       <c r="F741" t="n">
-        <v>3900</v>
+        <v>7000</v>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Spark</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -45969,7 +45969,7 @@
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>B66960171</t>
+          <t>36311</t>
         </is>
       </c>
       <c r="L741" t="inlineStr">
@@ -45979,7 +45979,7 @@
       </c>
       <c r="M741" t="inlineStr">
         <is>
-          <t>SMART ForTwo Cabriolet Rally A451 (2014), red</t>
+          <t>LINCOLN TownCar Limousine 2000, black</t>
         </is>
       </c>
       <c r="N741" t="inlineStr">
@@ -45993,30 +45993,34 @@
         <v>741</v>
       </c>
       <c r="B742" t="n">
-        <v>225421</v>
+        <v>188469</v>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Mini John Cooper Works WRC #37 (2012)</t>
+          <t>SMART ForTwo Cabriolet Rally A451 2014</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-13-at-022826.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-13-at-022826-2.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-13-at-022826-1.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-10-at-233229-3.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-10-at-233229-6.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-10-at-233229-5.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-10-at-233229-4.jpg</t>
         </is>
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>6999312</t>
+          <t>699691</t>
         </is>
       </c>
       <c r="F742" t="n">
-        <v>5500</v>
-      </c>
-      <c r="G742" t="inlineStr"/>
+        <v>3900</v>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Altaya</t>
+          <t>Spark</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -46031,7 +46035,7 @@
       </c>
       <c r="K742" t="inlineStr">
         <is>
-          <t>ATR005</t>
+          <t>B66960171</t>
         </is>
       </c>
       <c r="L742" t="inlineStr">
@@ -46041,7 +46045,7 @@
       </c>
       <c r="M742" t="inlineStr">
         <is>
-          <t>Mini John Cooper Works WRC #37 D.Sordo/C.Del Barrio Rally Monte-Carlo 2012</t>
+          <t>SMART ForTwo Cabriolet Rally A451 (2014), red</t>
         </is>
       </c>
       <c r="N742" t="inlineStr">
@@ -46055,34 +46059,30 @@
         <v>742</v>
       </c>
       <c r="B743" t="n">
-        <v>240618</v>
+        <v>225421</v>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>FORD Escort Mk.I Twin Cam #16  1968</t>
+          <t>Mini John Cooper Works WRC #37 (2012)</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012215-5.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012215-6.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012215-7.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-13-at-022826.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-13-at-022826-2.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-13-at-022826-1.jpg</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>7018990</t>
+          <t>6999312</t>
         </is>
       </c>
       <c r="F743" t="n">
-        <v>3400</v>
-      </c>
-      <c r="G743" t="inlineStr">
-        <is>
-          <t>Ford</t>
-        </is>
-      </c>
+        <v>5500</v>
+      </c>
+      <c r="G743" t="inlineStr"/>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Altaya</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -46097,7 +46097,7 @@
       </c>
       <c r="K743" t="inlineStr">
         <is>
-          <t>4672101</t>
+          <t>ATR005</t>
         </is>
       </c>
       <c r="L743" t="inlineStr">
@@ -46107,7 +46107,7 @@
       </c>
       <c r="M743" t="inlineStr">
         <is>
-          <t>FORD Escort Mk.I Twin Cam #16 Frank Gardner "Alan Mann Racing" BTCC Champion 1968</t>
+          <t>Mini John Cooper Works WRC #37 D.Sordo/C.Del Barrio Rally Monte-Carlo 2012</t>
         </is>
       </c>
       <c r="N743" t="inlineStr">
@@ -46121,34 +46121,34 @@
         <v>743</v>
       </c>
       <c r="B744" t="n">
-        <v>327040</v>
+        <v>240618</v>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>LANCIA Beta Montecarlo Turbo  №51 (1980)</t>
+          <t>FORD Escort Mk.I Twin Cam #16  1968</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221300-15-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221302-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221302-2-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221300-14-(2).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221302-1-(1).jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012215-5.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012215-6.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012215-7.jpg</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>7049948</t>
+          <t>7018990</t>
         </is>
       </c>
       <c r="F744" t="n">
-        <v>4800</v>
+        <v>3400</v>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>Lancia</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>Altaya</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -46161,7 +46161,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>4672101</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -46169,7 +46173,7 @@
       </c>
       <c r="M744" t="inlineStr">
         <is>
-          <t>LANCIA Beta Montecarlo Turbo №51 DRM (1980)</t>
+          <t>FORD Escort Mk.I Twin Cam #16 Frank Gardner "Alan Mann Racing" BTCC Champion 1968</t>
         </is>
       </c>
       <c r="N744" t="inlineStr">
@@ -46183,34 +46187,34 @@
         <v>744</v>
       </c>
       <c r="B745" t="n">
-        <v>248157</v>
+        <v>327040</v>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>​JEEP Wrangler 4x4 Winter Edition 2017</t>
+          <t>LANCIA Beta Montecarlo Turbo  №51 (1980)</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000420_233.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000427_317.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000421_634.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000416_969.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000423_192.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221300-15-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221302-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221302-2-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221300-14-(2).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221302-1-(1).jpg</t>
         </is>
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>7183045</t>
+          <t>7049948</t>
         </is>
       </c>
       <c r="F745" t="n">
-        <v>5000</v>
+        <v>4800</v>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>Jeep</t>
+          <t>Lancia</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>Greenlight Collectibles</t>
+          <t>Altaya</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -46223,11 +46227,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr">
-        <is>
-          <t>86151</t>
-        </is>
-      </c>
+      <c r="K745" t="inlineStr"/>
       <c r="L745" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -46235,7 +46235,7 @@
       </c>
       <c r="M745" t="inlineStr">
         <is>
-          <t>JEEP Wrangler 4x4 Winter Edition 2017 Xtreme Purple</t>
+          <t>LANCIA Beta Montecarlo Turbo №51 DRM (1980)</t>
         </is>
       </c>
       <c r="N745" t="inlineStr">
@@ -46249,34 +46249,34 @@
         <v>745</v>
       </c>
       <c r="B746" t="n">
-        <v>240619</v>
+        <v>248157</v>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>BMW M3 (E30) #11 1991</t>
+          <t>​JEEP Wrangler 4x4 Winter Edition 2017</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012214-2.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012214-3.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012214-4.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000420_233.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000427_317.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000421_634.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000416_969.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000423_192.jpg</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>7220941</t>
+          <t>7183045</t>
         </is>
       </c>
       <c r="F746" t="n">
-        <v>4200</v>
+        <v>5000</v>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>Jeep</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Greenlight Collectibles</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -46291,7 +46291,7 @@
       </c>
       <c r="K746" t="inlineStr">
         <is>
-          <t>4672102</t>
+          <t>86151</t>
         </is>
       </c>
       <c r="L746" t="inlineStr">
@@ -46301,7 +46301,7 @@
       </c>
       <c r="M746" t="inlineStr">
         <is>
-          <t>BMW M3 (E30) #11 Will Hoy "VL Motorsport" BTCC Champion 1991</t>
+          <t>JEEP Wrangler 4x4 Winter Edition 2017 Xtreme Purple</t>
         </is>
       </c>
       <c r="N746" t="inlineStr">
@@ -46315,34 +46315,34 @@
         <v>746</v>
       </c>
       <c r="B747" t="n">
-        <v>174357</v>
+        <v>240619</v>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>LAMBORGHINI Gallardo Superleggera</t>
+          <t>BMW M3 (E30) #11 1991</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220208_990.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220142_649.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220124_577.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220420_719.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220438_953.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220333_487.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220316_116.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012214-2.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012214-3.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012214-4.jpg</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>7250346</t>
+          <t>7220941</t>
         </is>
       </c>
       <c r="F747" t="n">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>Lamborghini</t>
+          <t>BMW</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Autoart</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -46357,7 +46357,7 @@
       </c>
       <c r="K747" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>4672102</t>
         </is>
       </c>
       <c r="L747" t="inlineStr">
@@ -46367,7 +46367,7 @@
       </c>
       <c r="M747" t="inlineStr">
         <is>
-          <t>LAMBORGHINI Gallardo Superleggera</t>
+          <t>BMW M3 (E30) #11 Will Hoy "VL Motorsport" BTCC Champion 1991</t>
         </is>
       </c>
       <c r="N747" t="inlineStr">
@@ -46381,34 +46381,34 @@
         <v>747</v>
       </c>
       <c r="B748" t="n">
-        <v>189538</v>
+        <v>174357</v>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>BMW Z1</t>
+          <t>LAMBORGHINI Gallardo Superleggera</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-4.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-5.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-3.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-7.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-2.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-6-(1).jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220208_990.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220142_649.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220124_577.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220420_719.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220438_953.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220333_487.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220316_116.jpg</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>7256165</t>
+          <t>7250346</t>
         </is>
       </c>
       <c r="F748" t="n">
-        <v>5500</v>
+        <v>4400</v>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>Lamborghini</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Minichamps</t>
+          <t>Autoart</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -46423,7 +46423,7 @@
       </c>
       <c r="K748" t="inlineStr">
         <is>
-          <t>400020101</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="L748" t="inlineStr">
@@ -46433,7 +46433,7 @@
       </c>
       <c r="M748" t="inlineStr">
         <is>
-          <t>BMW Z1 Magicviolett хорошая новая модель с подвижными деталями в родном боксе</t>
+          <t>LAMBORGHINI Gallardo Superleggera</t>
         </is>
       </c>
       <c r="N748" t="inlineStr">
@@ -46447,34 +46447,34 @@
         <v>748</v>
       </c>
       <c r="B749" t="n">
-        <v>221592</v>
+        <v>189538</v>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>LAMBORGHINI LM 002 4х4 1986</t>
+          <t>BMW Z1</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011337-9.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011337-8.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011337-10.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011337-7.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-4.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-5.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-3.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-7.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-2.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-6-(1).jpg</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>7315732</t>
+          <t>7256165</t>
         </is>
       </c>
       <c r="F749" t="n">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>Lamborghini</t>
+          <t>BMW</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Altaya</t>
+          <t>Minichamps</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46489,7 +46489,7 @@
       </c>
       <c r="K749" t="inlineStr">
         <is>
-          <t>LAM020</t>
+          <t>400020101</t>
         </is>
       </c>
       <c r="L749" t="inlineStr">
@@ -46499,7 +46499,7 @@
       </c>
       <c r="M749" t="inlineStr">
         <is>
-          <t>LAMBORGHINI LM 002 4х4 1986</t>
+          <t>BMW Z1 Magicviolett хорошая новая модель с подвижными деталями в родном боксе</t>
         </is>
       </c>
       <c r="N749" t="inlineStr">
@@ -46513,34 +46513,34 @@
         <v>749</v>
       </c>
       <c r="B750" t="n">
-        <v>366743</v>
+        <v>221592</v>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Berliet GBD 4X4 Fourgon-Pompe Tonne Hors Route Camiva</t>
+          <t>LAMBORGHINI LM 002 4х4 1986</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-05-at-223201.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-05-at-223201-1.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-05-at-223202.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011337-9.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011337-8.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011337-10.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011337-7.jpg</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>7417773</t>
+          <t>7315732</t>
         </is>
       </c>
       <c r="F750" t="n">
-        <v>3900</v>
+        <v>6000</v>
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>Berliet</t>
+          <t>Lamborghini</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Altaya</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -46555,7 +46555,7 @@
       </c>
       <c r="K750" t="inlineStr">
         <is>
-          <t>FC059</t>
+          <t>LAM020</t>
         </is>
       </c>
       <c r="L750" t="inlineStr">
@@ -46565,7 +46565,7 @@
       </c>
       <c r="M750" t="inlineStr">
         <is>
-          <t>Berliet GBD 4X4 Fourgon-Pompe Tonne Hors Route Camiva</t>
+          <t>LAMBORGHINI LM 002 4х4 1986</t>
         </is>
       </c>
       <c r="N750" t="inlineStr">
@@ -46579,30 +46579,34 @@
         <v>750</v>
       </c>
       <c r="B751" t="n">
-        <v>223706</v>
+        <v>366743</v>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Автоцистерна АЦ-30 (205)</t>
+          <t>Berliet GBD 4X4 Fourgon-Pompe Tonne Hors Route Camiva</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220608_187-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220451_903-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220507_925-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220517_630-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220505_167-(1).jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-05-at-223201.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-05-at-223201-1.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-05-at-223202.jpg</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>7453420</t>
+          <t>7417773</t>
         </is>
       </c>
       <c r="F751" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G751" t="inlineStr"/>
+        <v>3900</v>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>Berliet</t>
+        </is>
+      </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>Автолегенды СССР журнал от DeAgostini</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -46615,7 +46619,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>FC059</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -46623,7 +46631,7 @@
       </c>
       <c r="M751" t="inlineStr">
         <is>
-          <t>Автоцистерна АЦ-30 (205)</t>
+          <t>Berliet GBD 4X4 Fourgon-Pompe Tonne Hors Route Camiva</t>
         </is>
       </c>
       <c r="N751" t="inlineStr">
@@ -46637,30 +46645,30 @@
         <v>751</v>
       </c>
       <c r="B752" t="n">
-        <v>186677</v>
+        <v>223706</v>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Multiple Gun Motor Carriage M16</t>
+          <t>Автоцистерна АЦ-30 (205)</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230222.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230223.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230223-1.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220608_187-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220451_903-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220507_925-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220517_630-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220505_167-(1).jpg</t>
         </is>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>7487066</t>
+          <t>7453420</t>
         </is>
       </c>
       <c r="F752" t="n">
-        <v>3850</v>
+        <v>2200</v>
       </c>
       <c r="G752" t="inlineStr"/>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Автолегенды СССР журнал от DeAgostini</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46673,11 +46681,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr">
-        <is>
-          <t>6690003</t>
-        </is>
-      </c>
+      <c r="K752" t="inlineStr"/>
       <c r="L752" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -46685,7 +46689,7 @@
       </c>
       <c r="M752" t="inlineStr">
         <is>
-          <t>Multiple Gun Motor Carriage M16, military green</t>
+          <t>Автоцистерна АЦ-30 (205)</t>
         </is>
       </c>
       <c r="N752" t="inlineStr">
@@ -46699,34 +46703,30 @@
         <v>752</v>
       </c>
       <c r="B753" t="n">
-        <v>221606</v>
+        <v>186677</v>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN Golf I GTI 1976 White</t>
+          <t>Multiple Gun Motor Carriage M16</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012216-16.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012216-17.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012216-18.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230222.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230223.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230223-1.jpg</t>
         </is>
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>7508306</t>
+          <t>7487066</t>
         </is>
       </c>
       <c r="F753" t="n">
-        <v>3800</v>
-      </c>
-      <c r="G753" t="inlineStr">
-        <is>
-          <t>Volkswagen</t>
-        </is>
-      </c>
+        <v>3850</v>
+      </c>
+      <c r="G753" t="inlineStr"/>
       <c r="H753" t="inlineStr">
         <is>
-          <t>Altaya</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -46741,7 +46741,7 @@
       </c>
       <c r="K753" t="inlineStr">
         <is>
-          <t>TA003</t>
+          <t>6690003</t>
         </is>
       </c>
       <c r="L753" t="inlineStr">
@@ -46751,7 +46751,7 @@
       </c>
       <c r="M753" t="inlineStr">
         <is>
-          <t>VOLKSWAGEN Golf I GTI 1976 White</t>
+          <t>Multiple Gun Motor Carriage M16, military green</t>
         </is>
       </c>
       <c r="N753" t="inlineStr">
@@ -46765,29 +46765,29 @@
         <v>753</v>
       </c>
       <c r="B754" t="n">
-        <v>327718</v>
+        <v>221606</v>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Mercedes-Benz 300SLR #722</t>
+          <t>VOLKSWAGEN Golf I GTI 1976 White</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-28.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-29.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-30.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-31.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-27.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012216-16.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012216-17.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012216-18.jpg</t>
         </is>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>7616575</t>
+          <t>7508306</t>
         </is>
       </c>
       <c r="F754" t="n">
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>Volkswagen</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
@@ -46805,7 +46805,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>TA003</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -46813,7 +46817,7 @@
       </c>
       <c r="M754" t="inlineStr">
         <is>
-          <t>Mercedes-Benz 300SLR #722 победитель Mille Miglia 1955 Stilring Moss/Denis Jenkinson (средняя скорость 160км/ч)</t>
+          <t>VOLKSWAGEN Golf I GTI 1976 White</t>
         </is>
       </c>
       <c r="N754" t="inlineStr">
@@ -46827,25 +46831,25 @@
         <v>754</v>
       </c>
       <c r="B755" t="n">
-        <v>173083</v>
+        <v>327718</v>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ 300 SLR Racing Sports Car 1955</t>
+          <t>Mercedes-Benz 300SLR #722</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011339-18.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011339-19.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011339-20.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011339-21.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011339-17.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-28.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-29.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-30.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-31.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-27.jpg</t>
         </is>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>7710208</t>
+          <t>7616575</t>
         </is>
       </c>
       <c r="F755" t="n">
-        <v>3450</v>
+        <v>4000</v>
       </c>
       <c r="G755" t="inlineStr">
         <is>
@@ -46854,7 +46858,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>DeAgostini</t>
+          <t>Altaya</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -46875,7 +46879,7 @@
       </c>
       <c r="M755" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ 300 SLR Racing Sports Car (1955), Mercedes-Benz Offizielle Modell-Sammlung 32, silver</t>
+          <t>Mercedes-Benz 300SLR #722 победитель Mille Miglia 1955 Stilring Moss/Denis Jenkinson (средняя скорость 160км/ч)</t>
         </is>
       </c>
       <c r="N755" t="inlineStr">
@@ -46889,34 +46893,34 @@
         <v>755</v>
       </c>
       <c r="B756" t="n">
-        <v>397000</v>
+        <v>173083</v>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>​VOISIN Biscooter C-31 1957</t>
+          <t>MERCEDES-BENZ 300 SLR Racing Sports Car 1955</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234313_094.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234643_714.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234316_776.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234309_337.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234305_817.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234320_577.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011339-18.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011339-19.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011339-20.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011339-21.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011339-17.jpg</t>
         </is>
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>7769678</t>
+          <t>7710208</t>
         </is>
       </c>
       <c r="F756" t="n">
-        <v>3500</v>
+        <v>3450</v>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>Voisin</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>Altaya</t>
+          <t>DeAgostini</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -46929,11 +46933,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr">
-        <is>
-          <t>M2672-26</t>
-        </is>
-      </c>
+      <c r="K756" t="inlineStr"/>
       <c r="L756" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -46941,7 +46941,7 @@
       </c>
       <c r="M756" t="inlineStr">
         <is>
-          <t>VOISIN Biscooter C-31 (1957), Micro-Voitures d'Antan 26</t>
+          <t>MERCEDES-BENZ 300 SLR Racing Sports Car (1955), Mercedes-Benz Offizielle Modell-Sammlung 32, silver</t>
         </is>
       </c>
       <c r="N756" t="inlineStr">
@@ -46955,34 +46955,34 @@
         <v>756</v>
       </c>
       <c r="B757" t="n">
-        <v>348585</v>
+        <v>397000</v>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>OPEL Blitz M0bel-Werke Eiweilar Saar</t>
+          <t>​VOISIN Biscooter C-31 1957</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000706-1.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000706-2.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000707-1.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000706.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000707.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234313_094.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234643_714.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234316_776.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234309_337.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234305_817.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234320_577.jpg</t>
         </is>
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>7820786</t>
+          <t>7769678</t>
         </is>
       </c>
       <c r="F757" t="n">
-        <v>3250</v>
+        <v>3500</v>
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>Opel</t>
+          <t>Voisin</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>DeAgostini</t>
+          <t>Altaya</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
@@ -46990,8 +46990,16 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J757" t="inlineStr"/>
-      <c r="K757" t="inlineStr"/>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>M2672-26</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -46999,7 +47007,7 @@
       </c>
       <c r="M757" t="inlineStr">
         <is>
-          <t>OPEL Blitz M0bel-Werke Eiweilar Saar</t>
+          <t>VOISIN Biscooter C-31 (1957), Micro-Voitures d'Antan 26</t>
         </is>
       </c>
       <c r="N757" t="inlineStr">
@@ -47013,30 +47021,34 @@
         <v>757</v>
       </c>
       <c r="B758" t="n">
-        <v>155503</v>
+        <v>348585</v>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ G4 Francisco Franco 1934</t>
+          <t>OPEL Blitz M0bel-Werke Eiweilar Saar</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234827_382.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234817_976.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234831_408.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234915_733.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234846_582.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234908_315.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234837_787.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234821_522.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234904_469.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000706-1.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000706-2.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000707-1.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000706.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000707.jpg</t>
         </is>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>7884675</t>
+          <t>7820786</t>
         </is>
       </c>
       <c r="F758" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G758" t="inlineStr"/>
+        <v>3250</v>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>Minichamps</t>
+          <t>DeAgostini</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -47044,16 +47056,8 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J758" t="inlineStr">
-        <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
-      <c r="K758" t="inlineStr">
-        <is>
-          <t>436035600</t>
-        </is>
-      </c>
+      <c r="J758" t="inlineStr"/>
+      <c r="K758" t="inlineStr"/>
       <c r="L758" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -47061,7 +47065,7 @@
       </c>
       <c r="M758" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ G4 Francisco Franco, Political leader series 11</t>
+          <t>OPEL Blitz M0bel-Werke Eiweilar Saar</t>
         </is>
       </c>
       <c r="N758" t="inlineStr">
@@ -47075,34 +47079,30 @@
         <v>758</v>
       </c>
       <c r="B759" t="n">
-        <v>375117</v>
+        <v>155503</v>
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>MORRIS MINI MINOR Kultowe Auta 162,</t>
+          <t>MERCEDES-BENZ G4 Francisco Franco 1934</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251206_215504_969.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251206_215459_211.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251206_215501_994.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251206_215456_563.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234827_382.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234817_976.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234831_408.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234915_733.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234846_582.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234908_315.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234837_787.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234821_522.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234904_469.jpg</t>
         </is>
       </c>
       <c r="E759" t="inlineStr">
         <is>
-          <t>8101839</t>
+          <t>7884675</t>
         </is>
       </c>
       <c r="F759" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G759" t="inlineStr">
-        <is>
-          <t>Morris</t>
-        </is>
-      </c>
+        <v>9000</v>
+      </c>
+      <c r="G759" t="inlineStr"/>
       <c r="H759" t="inlineStr">
         <is>
-          <t>DeAgostini</t>
+          <t>Minichamps</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -47115,7 +47115,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>436035600</t>
+        </is>
+      </c>
       <c r="L759" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -47123,7 +47127,7 @@
       </c>
       <c r="M759" t="inlineStr">
         <is>
-          <t>MORRIS MINI MINOR Kultowe Auta 162,</t>
+          <t>MERCEDES-BENZ G4 Francisco Franco, Political leader series 11</t>
         </is>
       </c>
       <c r="N759" t="inlineStr">
@@ -47137,34 +47141,34 @@
         <v>759</v>
       </c>
       <c r="B760" t="n">
-        <v>182349</v>
+        <v>375117</v>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>АЦУ-10(52) 1978 г.</t>
+          <t>MORRIS MINI MINOR Kultowe Auta 162,</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-07-11-at-002341-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-07-11-at-002602-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-07-11-at-002611-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-07-11-at-002618-(1).jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251206_215504_969.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251206_215459_211.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251206_215501_994.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251206_215456_563.jpg</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>8181608</t>
+          <t>8101839</t>
         </is>
       </c>
       <c r="F760" t="n">
-        <v>8900</v>
+        <v>3000</v>
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>ГАЗ</t>
+          <t>Morris</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>DiP Models</t>
+          <t>DeAgostini</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -47177,11 +47181,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr">
-        <is>
-          <t>105232</t>
-        </is>
-      </c>
+      <c r="K760" t="inlineStr"/>
       <c r="L760" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -47189,7 +47189,7 @@
       </c>
       <c r="M760" t="inlineStr">
         <is>
-          <t>Модель хранилась в боксе. Лот выставлен на других площадках, уточняйте наличие.</t>
+          <t>MORRIS MINI MINOR Kultowe Auta 162,</t>
         </is>
       </c>
       <c r="N760" t="inlineStr">
@@ -47203,30 +47203,34 @@
         <v>760</v>
       </c>
       <c r="B761" t="n">
-        <v>464586</v>
+        <v>182349</v>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Local Motors Rally Fighter (2012)</t>
+          <t>АЦУ-10(52) 1978 г.</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260224_161948_852-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260224_162003_308.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260224_162011_706.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260224_161824_589-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260224_161848_637-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260226_005311_332-(1).jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-07-11-at-002341-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-07-11-at-002602-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-07-11-at-002611-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-07-11-at-002618-(1).jpg</t>
         </is>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>8270561</t>
+          <t>8181608</t>
         </is>
       </c>
       <c r="F761" t="n">
-        <v>5500</v>
-      </c>
-      <c r="G761" t="inlineStr"/>
+        <v>8900</v>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>ГАЗ</t>
+        </is>
+      </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>Altaya</t>
+          <t>DiP Models</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -47241,7 +47245,7 @@
       </c>
       <c r="K761" t="inlineStr">
         <is>
-          <t>M4069-36</t>
+          <t>105232</t>
         </is>
       </c>
       <c r="L761" t="inlineStr">
@@ -47251,7 +47255,7 @@
       </c>
       <c r="M761" t="inlineStr">
         <is>
-          <t>Local Motors Rally Fighter (2012)</t>
+          <t>Модель хранилась в боксе. Лот выставлен на других площадках, уточняйте наличие.</t>
         </is>
       </c>
       <c r="N761" t="inlineStr">
@@ -47265,34 +47269,30 @@
         <v>761</v>
       </c>
       <c r="B762" t="n">
-        <v>154086</v>
+        <v>464586</v>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>ЗИС (АМО)-2</t>
+          <t>Local Motors Rally Fighter (2012)</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220533_144.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220535_848.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220602_342.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220527_099.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260224_161948_852-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260224_162003_308.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260224_162011_706.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260224_161824_589-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260224_161848_637-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260226_005311_332-(1).jpg</t>
         </is>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>8294015</t>
+          <t>8270561</t>
         </is>
       </c>
       <c r="F762" t="n">
-        <v>1950</v>
-      </c>
-      <c r="G762" t="inlineStr">
-        <is>
-          <t>ЗиС</t>
-        </is>
-      </c>
+        <v>5500</v>
+      </c>
+      <c r="G762" t="inlineStr"/>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Наш Автопром</t>
+          <t>Altaya</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -47305,7 +47305,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K762" t="inlineStr"/>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>M4069-36</t>
+        </is>
+      </c>
       <c r="L762" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -47313,7 +47317,7 @@
       </c>
       <c r="M762" t="inlineStr">
         <is>
-          <t>ЗИС (АМО)-2</t>
+          <t>Local Motors Rally Fighter (2012)</t>
         </is>
       </c>
       <c r="N762" t="inlineStr">
@@ -47327,30 +47331,34 @@
         <v>762</v>
       </c>
       <c r="B763" t="n">
-        <v>348498</v>
+        <v>154086</v>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>VANWALL VW57 Formula 1  1957</t>
+          <t>ЗИС (АМО)-2</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-05-at-235227-4.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-05-at-235227-3.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-05-at-235228.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220533_144.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220535_848.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220602_342.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220527_099.jpg</t>
         </is>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>8363179</t>
+          <t>8294015</t>
         </is>
       </c>
       <c r="F763" t="n">
-        <v>2990</v>
-      </c>
-      <c r="G763" t="inlineStr"/>
+        <v>1950</v>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>ЗиС</t>
+        </is>
+      </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Altaya</t>
+          <t>Наш Автопром</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -47371,7 +47379,7 @@
       </c>
       <c r="M763" t="inlineStr">
         <is>
-          <t>VANWALL VW57 Formula 1Stiring Moss 1957</t>
+          <t>ЗИС (АМО)-2</t>
         </is>
       </c>
       <c r="N763" t="inlineStr">
@@ -47385,25 +47393,25 @@
         <v>763</v>
       </c>
       <c r="B764" t="n">
-        <v>440388</v>
+        <v>348498</v>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>​GOGGOMOBIL TL 400 - 1958</t>
+          <t>VANWALL VW57 Formula 1  1957</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234213_634.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234140_179.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234110_491.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234206_456.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-05-at-235227-4.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-05-at-235227-3.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-05-at-235228.jpg</t>
         </is>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>846277</t>
+          <t>8363179</t>
         </is>
       </c>
       <c r="F764" t="n">
-        <v>3600</v>
+        <v>2990</v>
       </c>
       <c r="G764" t="inlineStr"/>
       <c r="H764" t="inlineStr">
@@ -47421,11 +47429,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr">
-        <is>
-          <t>M2672-44</t>
-        </is>
-      </c>
+      <c r="K764" t="inlineStr"/>
       <c r="L764" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -47433,7 +47437,7 @@
       </c>
       <c r="M764" t="inlineStr">
         <is>
-          <t>GOGGOMOBIL TL 400 - 1958, Micro-Voitures d'Antan 44</t>
+          <t>VANWALL VW57 Formula 1Stiring Moss 1957</t>
         </is>
       </c>
       <c r="N764" t="inlineStr">
@@ -47447,34 +47451,30 @@
         <v>764</v>
       </c>
       <c r="B765" t="n">
-        <v>254037</v>
+        <v>440388</v>
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>​JEEP CJ-7 Renegade 4х4 1983</t>
+          <t>​GOGGOMOBIL TL 400 - 1958</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000407_167.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000405_387.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000341_393.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000326_109.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000407_167-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000412_689-(1).jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234213_634.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234140_179.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234110_491.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234206_456.jpg</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>8491610</t>
+          <t>846277</t>
         </is>
       </c>
       <c r="F765" t="n">
-        <v>4600</v>
-      </c>
-      <c r="G765" t="inlineStr">
-        <is>
-          <t>Jeep</t>
-        </is>
-      </c>
+        <v>3600</v>
+      </c>
+      <c r="G765" t="inlineStr"/>
       <c r="H765" t="inlineStr">
         <is>
-          <t>Greenlight Collectibles</t>
+          <t>Altaya</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -47489,7 +47489,7 @@
       </c>
       <c r="K765" t="inlineStr">
         <is>
-          <t>86533</t>
+          <t>M2672-44</t>
         </is>
       </c>
       <c r="L765" t="inlineStr">
@@ -47499,7 +47499,7 @@
       </c>
       <c r="M765" t="inlineStr">
         <is>
-          <t>JEEP CJ-7 Renegade 4х4 1983 (машина Сары Коннор из к/ф "Терминатор")</t>
+          <t>GOGGOMOBIL TL 400 - 1958, Micro-Voitures d'Antan 44</t>
         </is>
       </c>
       <c r="N765" t="inlineStr">
@@ -47513,34 +47513,34 @@
         <v>765</v>
       </c>
       <c r="B766" t="n">
-        <v>189066</v>
+        <v>254037</v>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>PORSCHE 934 #91 24h Le Mans 1980</t>
+          <t>​JEEP CJ-7 Renegade 4х4 1983</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011336-3.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011336-4.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011336-5.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011337.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011336-2.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011337-1.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000407_167.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000405_387.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000341_393.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000326_109.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000407_167-(1).jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251224_000412_689-(1).jpg</t>
         </is>
       </c>
       <c r="E766" t="inlineStr">
         <is>
-          <t>8590544</t>
+          <t>8491610</t>
         </is>
       </c>
       <c r="F766" t="n">
-        <v>7800</v>
+        <v>4600</v>
       </c>
       <c r="G766" t="inlineStr">
         <is>
-          <t>Porsche</t>
+          <t>Jeep</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>Premium X</t>
+          <t>Greenlight Collectibles</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -47555,7 +47555,7 @@
       </c>
       <c r="K766" t="inlineStr">
         <is>
-          <t>PR0417</t>
+          <t>86533</t>
         </is>
       </c>
       <c r="L766" t="inlineStr">
@@ -47565,7 +47565,7 @@
       </c>
       <c r="M766" t="inlineStr">
         <is>
-          <t>PORSCHE 934 #91 24h Le Mans 1980есть другие</t>
+          <t>JEEP CJ-7 Renegade 4х4 1983 (машина Сары Коннор из к/ф "Терминатор")</t>
         </is>
       </c>
       <c r="N766" t="inlineStr">
@@ -47579,34 +47579,34 @@
         <v>766</v>
       </c>
       <c r="B767" t="n">
-        <v>396798</v>
+        <v>189066</v>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ 500 SEL W126  1989</t>
+          <t>PORSCHE 934 #91 24h Le Mans 1980</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251231_000901_934.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251231_000858_102.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251231_000852_805.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251231_000730_668.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251231_000853_965.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251231_000900_979.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011336-3.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011336-4.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011336-5.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011337.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011336-2.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011337-1.jpg</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
         <is>
-          <t>8614264</t>
+          <t>8590544</t>
         </is>
       </c>
       <c r="F767" t="n">
-        <v>9800</v>
+        <v>7800</v>
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>Porsche</t>
         </is>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>Minichamps</t>
+          <t>Premium X</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
@@ -47619,7 +47619,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>PR0417</t>
+        </is>
+      </c>
       <c r="L767" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -47627,7 +47631,7 @@
       </c>
       <c r="M767" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ 500 SEL W126 Helmut Kohl (1989), silver</t>
+          <t>PORSCHE 934 #91 24h Le Mans 1980есть другие</t>
         </is>
       </c>
       <c r="N767" t="inlineStr">
@@ -47641,30 +47645,34 @@
         <v>767</v>
       </c>
       <c r="B768" t="n">
-        <v>397723</v>
+        <v>396798</v>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Rovin D4 1963</t>
+          <t>MERCEDES-BENZ 500 SEL W126  1989</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234250_715.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234254_169.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234258_169.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234301_635.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251231_000901_934.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251231_000858_102.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251231_000852_805.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251231_000730_668.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251231_000853_965.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251231_000900_979.jpg</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>8730208</t>
+          <t>8614264</t>
         </is>
       </c>
       <c r="F768" t="n">
-        <v>3400</v>
-      </c>
-      <c r="G768" t="inlineStr"/>
+        <v>9800</v>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Altaya</t>
+          <t>Minichamps</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -47677,11 +47685,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr">
-        <is>
-          <t>M2672-04</t>
-        </is>
-      </c>
+      <c r="K768" t="inlineStr"/>
       <c r="L768" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -47689,7 +47693,7 @@
       </c>
       <c r="M768" t="inlineStr">
         <is>
-          <t>Rovin D4 1954, Micro-Voitures d'Antan 4</t>
+          <t>MERCEDES-BENZ 500 SEL W126 Helmut Kohl (1989), silver</t>
         </is>
       </c>
       <c r="N768" t="inlineStr">
@@ -47703,31 +47707,27 @@
         <v>768</v>
       </c>
       <c r="B769" t="n">
-        <v>181009</v>
+        <v>397723</v>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ 240 D Long 1973</t>
+          <t>Rovin D4 1963</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-20.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-21.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-22.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-19.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234250_715.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234254_169.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234258_169.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234301_635.jpg</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>8764360</t>
+          <t>8730208</t>
         </is>
       </c>
       <c r="F769" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G769" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz</t>
-        </is>
-      </c>
+        <v>3400</v>
+      </c>
+      <c r="G769" t="inlineStr"/>
       <c r="H769" t="inlineStr">
         <is>
           <t>Altaya</t>
@@ -47743,7 +47743,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>M2672-04</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -47751,7 +47755,7 @@
       </c>
       <c r="M769" t="inlineStr">
         <is>
-          <t>MERCEDES-BENZ 240 D Long (1973)</t>
+          <t>Rovin D4 1954, Micro-Voitures d'Antan 4</t>
         </is>
       </c>
       <c r="N769" t="inlineStr">
@@ -47765,29 +47769,29 @@
         <v>769</v>
       </c>
       <c r="B770" t="n">
-        <v>197683</v>
+        <v>181009</v>
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>MASERATI Tipo 61 #78 1961</t>
+          <t>MERCEDES-BENZ 240 D Long 1973</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230055.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230056.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230054.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230057.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230055-1.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-20.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-21.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-22.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-29-at-011338-19.jpg</t>
         </is>
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>8805103</t>
+          <t>8764360</t>
         </is>
       </c>
       <c r="F770" t="n">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>Maserati</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="H770" t="inlineStr">
@@ -47805,11 +47809,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K770" t="inlineStr">
-        <is>
-          <t>MA062</t>
-        </is>
-      </c>
+      <c r="K770" t="inlineStr"/>
       <c r="L770" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -47817,7 +47817,7 @@
       </c>
       <c r="M770" t="inlineStr">
         <is>
-          <t>MASERATI Tipo 61 #78 Schroeder Nassau Trophy 1961</t>
+          <t>MERCEDES-BENZ 240 D Long (1973)</t>
         </is>
       </c>
       <c r="N770" t="inlineStr">
@@ -47831,29 +47831,29 @@
         <v>770</v>
       </c>
       <c r="B771" t="n">
-        <v>185683</v>
+        <v>197683</v>
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>Seat Cordoba WRC #2 (2001)</t>
+          <t>MASERATI Tipo 61 #78 1961</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-13-at-022720-1.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-13-at-022720-4.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-13-at-022720-3.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230055.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230056.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230054.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230057.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-11-03-at-230055-1.jpg</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>896156</t>
+          <t>8805103</t>
         </is>
       </c>
       <c r="F771" t="n">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>SEAT</t>
+          <t>Maserati</t>
         </is>
       </c>
       <c r="H771" t="inlineStr">
@@ -47871,7 +47871,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>MA062</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -47879,7 +47883,7 @@
       </c>
       <c r="M771" t="inlineStr">
         <is>
-          <t>Seat Cordoba WRC #2 Rally RAC Navarra de Tierra, 2001</t>
+          <t>MASERATI Tipo 61 #78 Schroeder Nassau Trophy 1961</t>
         </is>
       </c>
       <c r="N771" t="inlineStr">
@@ -47893,29 +47897,29 @@
         <v>771</v>
       </c>
       <c r="B772" t="n">
-        <v>225471</v>
+        <v>185683</v>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>LAMBORGHINI Diablo VT-R Roadster Trofeo 1997</t>
+          <t>Seat Cordoba WRC #2 (2001)</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234324_300.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234640_247.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234634_264.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234638_048.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234631_600.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234625_500.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234641_985.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234627_491.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-13-at-022720-1.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-13-at-022720-4.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-13-at-022720-3.jpg</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>9017121</t>
+          <t>896156</t>
         </is>
       </c>
       <c r="F772" t="n">
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>Lamborghini</t>
+          <t>SEAT</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
@@ -47933,11 +47937,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K772" t="inlineStr">
-        <is>
-          <t>LAM052</t>
-        </is>
-      </c>
+      <c r="K772" t="inlineStr"/>
       <c r="L772" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -47945,7 +47945,7 @@
       </c>
       <c r="M772" t="inlineStr">
         <is>
-          <t>LAMBORGHINI Diablo VT-R Roadster Trofeo 1997</t>
+          <t>Seat Cordoba WRC #2 Rally RAC Navarra de Tierra, 2001</t>
         </is>
       </c>
       <c r="N772" t="inlineStr">
@@ -47959,27 +47959,31 @@
         <v>772</v>
       </c>
       <c r="B773" t="n">
-        <v>317708</v>
+        <v>225471</v>
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>FIAT 125 Mirafiori 1981</t>
+          <t>LAMBORGHINI Diablo VT-R Roadster Trofeo 1997</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220203_741.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220307_178.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220126_625.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220430_080.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220342_780.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220330_259.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220252_274.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234324_300.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234640_247.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234634_264.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234638_048.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234631_600.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234625_500.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234641_985.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20251208_234627_491.jpg</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>9127780</t>
+          <t>9017121</t>
         </is>
       </c>
       <c r="F773" t="n">
-        <v>2300</v>
-      </c>
-      <c r="G773" t="inlineStr"/>
+        <v>4000</v>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>Lamborghini</t>
+        </is>
+      </c>
       <c r="H773" t="inlineStr">
         <is>
           <t>Altaya</t>
@@ -47995,7 +47999,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>LAM052</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -48003,7 +48011,7 @@
       </c>
       <c r="M773" t="inlineStr">
         <is>
-          <t>FIAT 125 Mirafiori (1981)надломано переднее левое колесо</t>
+          <t>LAMBORGHINI Diablo VT-R Roadster Trofeo 1997</t>
         </is>
       </c>
       <c r="N773" t="inlineStr">
@@ -48017,31 +48025,27 @@
         <v>773</v>
       </c>
       <c r="B774" t="n">
-        <v>257979</v>
+        <v>317708</v>
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Seat Ibiza GTI Kit Car #24 (1999)</t>
+          <t>FIAT 125 Mirafiori 1981</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221300-7.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221300-8.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221300-9.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220203_741.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220307_178.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220126_625.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220430_080.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220342_780.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220330_259.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260526_220252_274.jpg</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>9131472</t>
+          <t>9127780</t>
         </is>
       </c>
       <c r="F774" t="n">
-        <v>4200</v>
-      </c>
-      <c r="G774" t="inlineStr">
-        <is>
-          <t>SEAT</t>
-        </is>
-      </c>
+        <v>2300</v>
+      </c>
+      <c r="G774" t="inlineStr"/>
       <c r="H774" t="inlineStr">
         <is>
           <t>Altaya</t>
@@ -48065,7 +48069,7 @@
       </c>
       <c r="M774" t="inlineStr">
         <is>
-          <t>Seat Ibiza GTI Kit Car #24 Rally Monte-Carlo (1999)</t>
+          <t>FIAT 125 Mirafiori (1981)надломано переднее левое колесо</t>
         </is>
       </c>
       <c r="N774" t="inlineStr">
@@ -48079,34 +48083,34 @@
         <v>774</v>
       </c>
       <c r="B775" t="n">
-        <v>176461</v>
+        <v>257979</v>
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Уральский 375Д бортовой с тентом</t>
+          <t>Seat Ibiza GTI Kit Car #24 (1999)</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-10-29-at-234457-5.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-10-29-at-234457-7.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-10-29-at-234457-4.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-07-08-at-233410-(1).jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221300-7.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221300-8.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-12-at-221300-9.jpg</t>
         </is>
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>9192234</t>
+          <t>9131472</t>
         </is>
       </c>
       <c r="F775" t="n">
-        <v>4350</v>
+        <v>4200</v>
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>УРАЛ</t>
+          <t>SEAT</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Altaya</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -48119,11 +48123,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K775" t="inlineStr">
-        <is>
-          <t>SSM1103</t>
-        </is>
-      </c>
+      <c r="K775" t="inlineStr"/>
       <c r="L775" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -48131,7 +48131,7 @@
       </c>
       <c r="M775" t="inlineStr">
         <is>
-          <t>Уральский 375Д бортовой с тентом, голубой</t>
+          <t>Seat Ibiza GTI Kit Car #24 Rally Monte-Carlo (1999)</t>
         </is>
       </c>
       <c r="N775" t="inlineStr">
@@ -48145,34 +48145,34 @@
         <v>775</v>
       </c>
       <c r="B776" t="n">
-        <v>189538</v>
+        <v>176461</v>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Mersedes-Benz CLS 350</t>
+          <t>Уральский 375Д бортовой с тентом</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-15.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-19.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-16.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-17.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-14.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-18.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-10-29-at-234457-5.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-10-29-at-234457-7.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-10-29-at-234457-4.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-07-08-at-233410-(1).jpg</t>
         </is>
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>9579352</t>
+          <t>9192234</t>
         </is>
       </c>
       <c r="F776" t="n">
-        <v>5600</v>
+        <v>4350</v>
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>УРАЛ</t>
         </is>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Norev</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -48187,7 +48187,7 @@
       </c>
       <c r="K776" t="inlineStr">
         <is>
-          <t>400020101</t>
+          <t>SSM1103</t>
         </is>
       </c>
       <c r="L776" t="inlineStr">
@@ -48197,7 +48197,7 @@
       </c>
       <c r="M776" t="inlineStr">
         <is>
-          <t>Mersedes-Benz CLS 350 от Norel</t>
+          <t>Уральский 375Д бортовой с тентом, голубой</t>
         </is>
       </c>
       <c r="N776" t="inlineStr">
@@ -48211,34 +48211,34 @@
         <v>776</v>
       </c>
       <c r="B777" t="n">
-        <v>174204</v>
+        <v>189538</v>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>RANGE ROVER Sport Casino Royale (2006)</t>
+          <t>Mersedes-Benz CLS 350</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012216-23.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012216-24.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012216-25.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-15.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-19.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-16.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-17.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-14.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-04-at-000223-18.jpg</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>9661295</t>
+          <t>9579352</t>
         </is>
       </c>
       <c r="F777" t="n">
-        <v>3500</v>
+        <v>5600</v>
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>Rover</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>Eaglemoss</t>
+          <t>Norev</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -48253,7 +48253,7 @@
       </c>
       <c r="K777" t="inlineStr">
         <is>
-          <t>JB51</t>
+          <t>400020101</t>
         </is>
       </c>
       <c r="L777" t="inlineStr">
@@ -48263,7 +48263,7 @@
       </c>
       <c r="M777" t="inlineStr">
         <is>
-          <t>RANGE ROVER Sport Casino Royale (2006), metallic gold</t>
+          <t>Mersedes-Benz CLS 350 от Norel</t>
         </is>
       </c>
       <c r="N777" t="inlineStr">
@@ -48277,34 +48277,34 @@
         <v>777</v>
       </c>
       <c r="B778" t="n">
-        <v>155500</v>
+        <v>174204</v>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Alfa Romeo 8C 2900 B Lungo 1938</t>
+          <t>RANGE ROVER Sport Casino Royale (2006)</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_235004_019.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234956_550.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_235011_631.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_235000_296.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234952_900.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_235015_299.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_235032_770.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_235025_966.jpg</t>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012216-23.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012216-24.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012216-25.jpg</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>9711764</t>
+          <t>9661295</t>
         </is>
       </c>
       <c r="F778" t="n">
-        <v>9500</v>
+        <v>3500</v>
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>Alfa Romeo</t>
+          <t>Rover</t>
         </is>
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>Minichamps</t>
+          <t>Eaglemoss</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -48319,7 +48319,7 @@
       </c>
       <c r="K778" t="inlineStr">
         <is>
-          <t>TSMCE154313</t>
+          <t>JB51</t>
         </is>
       </c>
       <c r="L778" t="inlineStr">
@@ -48329,7 +48329,7 @@
       </c>
       <c r="M778" t="inlineStr">
         <is>
-          <t>Alfa Romeo 8C 2900 B Lungo Touring Carrozzeria Superleggera</t>
+          <t>RANGE ROVER Sport Casino Royale (2006), metallic gold</t>
         </is>
       </c>
       <c r="N778" t="inlineStr">
@@ -48343,62 +48343,194 @@
         <v>778</v>
       </c>
       <c r="B779" t="n">
+        <v>155500</v>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Alfa Romeo 8C 2900 B Lungo 1938</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_235004_019.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234956_550.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_235011_631.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_235000_296.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_234952_900.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_235015_299.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_235032_770.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/img_20260505_235025_966.jpg</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>9711764</t>
+        </is>
+      </c>
+      <c r="F779" t="n">
+        <v>9500</v>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>Alfa Romeo</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>Minichamps</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>TSMCE154313</t>
+        </is>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M779" t="inlineStr">
+        <is>
+          <t>Alfa Romeo 8C 2900 B Lungo Touring Carrozzeria Superleggera</t>
+        </is>
+      </c>
+      <c r="N779" t="inlineStr">
+        <is>
+          <t>Россия, Хабаровский край, Хабаровск</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="n">
+        <v>779</v>
+      </c>
+      <c r="B780" t="n">
+        <v>184756</v>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>MITSUBISHI LANCER EVOLUTION X - #61</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012217-1.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012217-4.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012217-3.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012217-2.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-08-12-at-012217.jpg</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>9864273</t>
+        </is>
+      </c>
+      <c r="F780" t="n">
+        <v>6100</v>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>Mitsubishi</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>43428</t>
+        </is>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>MITSUBISHI LANCER EVOLUTION X - #61 F.Nutahara/T.Sato</t>
+        </is>
+      </c>
+      <c r="N780" t="inlineStr">
+        <is>
+          <t>Россия, Хабаровский край, Хабаровск</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="n">
+        <v>780</v>
+      </c>
+      <c r="B781" t="n">
         <v>8091</v>
       </c>
-      <c r="C779" t="inlineStr">
+      <c r="C781" t="inlineStr">
         <is>
           <t>ROCAR TV 12F</t>
         </is>
       </c>
-      <c r="D779" t="inlineStr">
+      <c r="D781" t="inlineStr">
         <is>
           <t>https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-08-at-012435-1.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-08-at-012435-2.jpg; https://scalebay.ru/uploads/user/s/a/sanya-kuznec_7522/whatsapp-image-2025-09-08-at-012436.jpg</t>
         </is>
       </c>
-      <c r="E779" t="inlineStr">
+      <c r="E781" t="inlineStr">
         <is>
           <t>9896814</t>
         </is>
       </c>
-      <c r="F779" t="n">
+      <c r="F781" t="n">
         <v>2050</v>
       </c>
-      <c r="G779" t="inlineStr">
+      <c r="G781" t="inlineStr">
         <is>
           <t>Rocar</t>
         </is>
       </c>
-      <c r="H779" t="inlineStr">
+      <c r="H781" t="inlineStr">
         <is>
           <t>DeAgostini</t>
         </is>
       </c>
-      <c r="I779" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="J779" t="inlineStr">
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J781" t="inlineStr">
         <is>
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr">
+      <c r="K781" t="inlineStr">
         <is>
           <t>mas017</t>
         </is>
       </c>
-      <c r="L779" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="M779" t="inlineStr">
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M781" t="inlineStr">
         <is>
           <t>ROCAR TV 12F, Masini de Legenda 17, yellow№ 17 из серии Мașini de legendă</t>
         </is>
       </c>
-      <c r="N779" t="inlineStr">
+      <c r="N781" t="inlineStr">
         <is>
           <t>Россия, Хабаровский край, Хабаровск</t>
         </is>

--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -413,298 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ID UNOMAG</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Название</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Фото (ссылки)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Лот №</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Единая цена</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Марка</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Производитель</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Масштаб</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Материал</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Артикул</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Состояние</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Описание</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Местоположение</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>226818</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Mercedes Brabus 850 6.0 Widestar  2016 Minichamps</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20260202_134535.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20260202_134448.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20260202_134541.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20260202_134547.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20260202_134601.jpg</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4213802</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Minichamps</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Б/у</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>В связи с колебаниями курса рубля, необходимо уточнять цену перед покупкой.Отправляю по всему миру - по возможности.</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>176749</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Mercedes Brabus G  V12 Widestar 2010  Minichamps</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175143.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175106.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175136.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175148.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175203.jpg</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>7151583</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Brabus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Minichamps</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Б/у</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>В связи с колебаниями курса рубля, необходимо уточнять цену перед покупкой.Отправляю по всему миру - по возможности.</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>214388</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Audi RS4 RS 4 Avant  2018 Spark</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471219.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471242.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471236.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471229.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471223.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471213.jpg</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>9331546</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>9600</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Audi</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Spark</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>В связи с колебаниями курса рубля, необходимо уточнять цену перед покупкой.Привезу любые модели на заказ.</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>484586</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Skoda 706 RTTN с полуприцепом Alka N12CH   АИСТ</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-2.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-3.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-8.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-9.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-6.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-7.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-5.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-10.jpg</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>7409184</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>4100</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Škoda</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Автоистория (АИСТ)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>металл , пластик, резина</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Информация по оплате и отправке в разделе " Обо мне". Условия аукциона стандартные. выход на связь в течении 3 дней оплата в течении 7 дней с момента окончания аукциона. Все вопросы по лоту , оплате , отправке исключительно до покупки (до ставки) Смотрите мои другие лоты.</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -413,9 +413,198 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID UNOMAG</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Фото (ссылки)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Лот №</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Единая цена</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Масштаб</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Артикул</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Состояние</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Местоположение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>234689</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mercedes X-Class 2017</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/mercedes-x-klasse-norev-183421-6.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202209.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202532.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202227.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202414.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202238.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202319.jpg</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4439325</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>9598</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Norev</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1:18</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>652272</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>КамАЗ-6522 самосвал белый</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-2.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-1.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-4.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-3.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-7.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-5.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-8.jpg</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1613562</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>104165</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Модель новая в оригинальной упаковке.Самовывоз в Москве от метро Строгино.Почта России или СДЭК от 500 рублей.Выход на связь 1 день, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -413,198 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ID UNOMAG</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Название</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Фото (ссылки)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Лот №</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Единая цена</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Марка</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Производитель</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Масштаб</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Материал</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Артикул</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Состояние</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Описание</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Местоположение</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>234689</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Mercedes X-Class 2017</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/mercedes-x-klasse-norev-183421-6.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202209.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202532.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202227.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202414.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202238.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202319.jpg</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4439325</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>9598</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Norev</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1:18</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>652272</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>КамАЗ-6522 самосвал белый</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-2.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-1.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-4.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-3.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-7.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-5.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-8.jpg</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1613562</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>4200</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>КамАЗ</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ПАО КАМАЗ</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>104165</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Модель новая в оригинальной упаковке.Самовывоз в Москве от метро Строгино.Почта России или СДЭК от 500 рублей.Выход на связь 1 день, оплата на карту Альфа банка 5 дней.</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -413,9 +413,6380 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID UNOMAG</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Фото (ссылки)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Лот №</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Единая цена</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Масштаб</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Артикул</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Состояние</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Местоположение</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Наличие</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>356447</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>КАМАЗ-54901 с полуприцепом НЕФАЗ-93341</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/932-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/931-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/933-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/935-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/934-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/937.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/936.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/938.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/939.jpg</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>10001182</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>707012</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>КММ-2 (51)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-2.jpg</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10001183</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>509635</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>КО-829А (4333) поливалка</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-8.jpg</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>10001581</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>655982</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>КАМАЗ-6520 серый</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-8.jpg</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10001778</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>507464</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Автобус Икарус-250.58 Интурбюро</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055945.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055951.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055955_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055959.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060002_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060008.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060019.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060133_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060150_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10001836</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>10200</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>557768</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Троллейбус ЗИУ-5 белый</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112604_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112614_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112611_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112608.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112630.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1-(2).jpg</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1062271</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ЗиУ</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>342834</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Автобус ЛиАЗ-677М бело-желтый СОВА</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-6-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1149836</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>483603</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>KAMAZ-65801-T5 самосвал</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-6-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-7-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-8-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1159045</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>7100</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SSM1547</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>694057</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ПУ-20 (51А)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-6.jpg</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1314693</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>221707</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ГЗСА-3711 (53) Почтовый фургон</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/gtk-32-51-657585-5.jpg</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1343751</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SSM1341</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>414794</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Контейнерный мусоровоз M-30 (53)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-11.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-12.jpg</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1388338</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>6100</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>501164</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Автобус Икарус 255.70 антик</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/1-50.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/2-39.jpg</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1440090</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>7100</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>588725</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Автобус Икарус-238</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/nashi-avtobusy-50-laz-697n-turist-110378-6.jpg</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1809086</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>10250</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ModelPro</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0264MP</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>207965</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>БЕЛАЗ-7522 (ранний) карьерный самосвал песочный</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-653275-8.jpg</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2066781</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>БелАЗ</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SSM1313</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>630928</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>KAMAZ-65225 жёлтый</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-8.jpg</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2075191</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>5300</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>159743</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Большой бокс SSM (32x10.5x10.5 см)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/bolshoy-boks-ssm-32x105x105-sm-14917-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2342651</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Пластмасса</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Бокс новыйСамовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>636031</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>СБ-92 (5511) серый бетоносмеситель</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-6.jpg</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2362962</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>214442</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>КРАЗ-214 Мосгортранс</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/241-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/242-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/243-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/244-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/248.jpg</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2428141</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2750</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>КрАЗ</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>472680</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Автобус Икарус 55.14 Ставрополь</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135027_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135038.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135049_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135057_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135107_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135117_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135129.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135143_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135202.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135309_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135323_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135345_1.jpg</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2532465</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>6300</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>655467</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Трамвай Tatra-T3SU синий</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-5.jpg</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2582990</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>7300</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>557767</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Троллейбус ЗИУ-5 красный</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112433.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112444_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112437_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112441_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112455_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2624588</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ЗиУ</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>488956</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Троллейбус ТГ-3</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-6-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-2.jpg</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2771714</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ТГ</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>223983</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>МАЗ-5550 Мосметро</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-6-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-10-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-8-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-9-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-16.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-3-1.jpg</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3096000</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>МАЗ</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>464451</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ПР-53 (52)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-6.jpg</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3114877</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>441039</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Пескоразбрасыватель ПР-53 (52)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/213-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/211-(3).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/212-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/214-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/215-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/216-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3161825</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>4450</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>6463</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Тигр 233001 пикап песочный</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/233001-pikap-11486-1-1.jpg</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3163203</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>189569</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>КАвЗ-3976 (бело-голубой)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240.jpg</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>321488</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>КАвЗ</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>SSM4017</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>621961</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>АКПМ-3 (130)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-6.jpg</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3229352</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>483604</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Автобус Икарус-280 красный</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-6.jpg</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3342857</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>5300</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>280346</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ЗИЛ-ММЗ-585Л самосвал</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-13.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-14.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-9.jpg</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3430175</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ММЗ</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>457283</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>КАМАЗ-65951 самосвал</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-7.jpg</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3466651</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>SSM1533</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>518058</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>БЕЦЕМА АЦ/АТЗ (KAMAZ-65207-87)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-9.jpg</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3563754</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>4250</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>500143</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Автобус Икарус 255.70 красный</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160531_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160540.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160536-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160543_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160547_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160554_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160652_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160710.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160731_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160744.jpg</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3785921</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>460540</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Автобус Икарус-260.06</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-6.jpg</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>4069148</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3100</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>441302</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Автобус Икарус 256.54 скарлат</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122158.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122209.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122223_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122220_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122213_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122217_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122229.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122237.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122401.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122422_1.jpg</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>4097841</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>15300</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>291330</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Skoda 706 MTTN с полуприцепом Alka N12CH Schlossberg Sekt</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-9.jpg</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>4178680</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>7800</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Škoda</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>507463</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Автобус Икарус-250.58 белый</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055133.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055138.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055143.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055146_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055151.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055156_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055204_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055312_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055329_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351.jpg</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>419962</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>10300</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>199553</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>КАЗ-ММЗ-4502 самосвал</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-15.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-16.jpg</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4250260</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ММЗ</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>SSM1293</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>584696</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>КАМАЗ-6520 рестайлинг самосвал</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-7-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-8-1-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4256288</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>8300</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>326092</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>КАМАЗ-54901 с п/п НЕФАЗ-93341 белый</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/902-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/901-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/904.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/903-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/905.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/907.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/906.jpg</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4381093</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>326092</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>КАМАЗ-54901 с полуприцепом НЕФАЗ-93341</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-11.jpg</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4386018</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>5900</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>722938</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Volvo F12 с полуприцепом Fruehauf Savoyarde белая/синяя</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f89-s-polupricepom-fruehauf-savoyarde-117743-3.jpg</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4386166</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>8250</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Volvo</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>SSM7077</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>696912</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Икарус 222 светло зеленый</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-5.jpg</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>4775954</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>10250</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ModelPro</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Смола</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>654956</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>KAMAZ-65225 (рестайлинг)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294.jpg</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4849168</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>198946</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>КРАЗ-257Б1 контейнер</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-10.jpg</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4910920</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>КрАЗ</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>SSM4017</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>633016</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>КАМАЗ-5511 самосвал темно-зеленый</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-6.jpg</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>4912801</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>486148</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>АК-75В (130)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-2-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-7-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-8-3.jpg</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>4986574</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>6250</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>SSM1549</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>472677</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>КАвЗ-651 рапсодия</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/5-18.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/2-23.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/4-19.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/3-20.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/1-30.jpg</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>5014580</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>КАвЗ</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>707012</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>КММ-2 (51)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-9.jpg</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>5048762</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Бачки</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>477641</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ikarus-280.64 оранжевый</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-6.jpg</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>5054284</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="n">
+        <v>588726</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>КАМАЗ-6522 рестайлинг желтый</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-7.jpg</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>5085617</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="n">
+        <v>153285</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ЗИС-151 бортовой темно зеленый</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-9.jpg</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>5172843</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2450</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ЗиС</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="n">
+        <v>459312</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ЗИЛ-4333 KО-829А поливалка</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-10.jpg</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>5294623</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>499998</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>МКМ-2 (4333)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-6-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-7-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>5463365</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="n">
+        <v>470904</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tatra-815S3 самосвал оранжевый/синий</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-8.jpg</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>5711242</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>6250</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>SSM1538</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="n">
+        <v>488484</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Бокс 32 см (32х9х9) DEMPRICE с винтами</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101849.jpg</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>6122001</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Пластмасса</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Бокс новый.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="n">
+        <v>150038</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ЗИЛ-130-76 бортовой (поздняя облицовка радиатора)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-6.jpg</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>6217765</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>2450</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>SSM1003</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>487535</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>KAMAЗ-43253 Рестайлинг</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-8.jpg</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>6249403</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>5650</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="n">
+        <v>640208</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>КАМАЗ-43118 рестайлинг</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-8.jpg</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>639065</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="n">
+        <v>641239</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>КАМАЗ-6520 Рестайлинг зеленый</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-8.jpg</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>6440694</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>473852</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Икарус 250.70 Чили ИНТУРИСТ DEMPRICE</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184241_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184254_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184312_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184333_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184354_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184415.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184450_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184950_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184840_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_185157_1.jpg</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>6455073</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>15300</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>342832</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Автобус ЛиАЗ-677М бело-синий СОВА</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-6-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>6498567</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>334587</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Прицеп МАЗ-8926</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-7.jpg</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>6762234</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>МАЗ</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>474035</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Икарус 250.70 клубничный ИНТУРИСТ</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173347.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173351_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173403.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173413.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173417_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173528.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173603_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173612.jpg</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>6773621</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>15300</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="n">
+        <v>519214</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>KAMAZ-6520-21010-53 самосвал</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-9.jpg</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>7206133</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>4250</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="n">
+        <v>205299</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>КрАЗ-6322 БРО-200</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-11.jpg</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>7250974</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>2050</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>КрАЗ</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Наш Автопром</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Н947</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="n">
+        <v>507465</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Автобус Икарус-250.58 Совтрансавто</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060555.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060600_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060606_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060611.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060615.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060619_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060627_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060740_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060800.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351-(2).jpg</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>7322725</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>15300</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="n">
+        <v>564883</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>KAMAZ-65952 самосвал</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-7.jpg</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>7408909</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="n">
+        <v>7575</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ЗИЛ-130 бортовой (ранняя облицовка радиатора)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-6.jpg</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>7424562</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>499198</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Икарус-280 белый с красной полосой</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-6.jpg</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>7438713</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="n">
+        <v>460537</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ЗИЛ-4333 КО-829А пескоразбрасыватель</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-7.jpg</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>745858</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>SSM1520</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
+        <v>519215</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>KAMAZ-65207-87 (S5) бортовой</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-8.jpg</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>7494811</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>693380</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Volvo F12 с полуприцепом Lamberet</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-10.jpg</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>7567444</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>12800</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Volvo</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>177912</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Полуприцеп МАЗ-5215 зелёный</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-4-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>7640294</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>МАЗ</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>SSM7011</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="n">
+        <v>183350</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ЯАЗ-205 самосвал зеленый</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-14.jpg</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>7644570</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ЯАЗ</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>474047</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Автобус Икарус 280.33 г. Орёл</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141310.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141318_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141322.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141330_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141335_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141340.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141352_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141456.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141651.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141816.jpg</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>7680062</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>15300</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>477068</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>КамАЗ-65802-87 (S5)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-9-1.jpg</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>7722142</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>7150</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>SSM1546</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="n">
+        <v>657404</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>КамАЗ-6522 оранжевый</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-8.jpg</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>785738</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>4250</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="n">
+        <v>441961</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Мусоровоз КО-413 (53) SSM</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/d5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d9.jpg</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>7902021</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>4650</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="n">
+        <v>495095</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PETERBILT 350</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250313_142201.jpg</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>8339384</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>4150</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Peterbilt</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>IXO грузовики (серии TRU)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="n">
+        <v>630206</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Norba KI-12 (5334) мусоровоз</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-8.jpg</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>8843536</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>6250</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>МАЗ</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="n">
+        <v>364917</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>КАМАЗ-65206 с полуприцепом НЕФАЗ-93341</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/954.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/952.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/951.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/953.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/955.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/956.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/957.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/958.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/959.jpg</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>8845471</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>7900</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>102972</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="n">
+        <v>472681</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Автобус ЛАЗ-695Н бело-красный</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111725.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111705_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111702.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111708_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111711_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111220_1-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>8879921</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ЛАЗ</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="n">
+        <v>472729</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tatra 815 V26 бортовая с тентом</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0021.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0023.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0022.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0024.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0025.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0026.jpg</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>8914544</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>5750</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="n">
+        <v>469263</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tatra-815S1 самосвал красный</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-9.jpg</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>9007302</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>5750</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>SSM1537</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="n">
+        <v>214234</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ГЗСА-893А (52) Мебельный фургон</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-12-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-13-1.jpg</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>9039863</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>2750</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>SSM1330</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="n">
+        <v>491552</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Троллейбус Skoda-9TR</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-6.jpg</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>9103969</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>3050</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Škoda</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="n">
+        <v>516931</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>КамАЗ-65802-87 (S5) самосвал</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-9-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-10-1.jpg</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>9158455</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="n">
+        <v>695471</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Полуприцеп НАМИ-790</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-2.jpg</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>9199667</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>НАМИ</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>473509</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Автобус Икарус 256.54 Киноварь</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191021_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191025_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191029.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191032_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191036.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191048_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191107_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191147_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191207_1.jpg</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>92437</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>9300</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="n">
+        <v>473515</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ЛиАЗ-5256 турмалин желто-белый</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163716.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163720_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163746.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163741_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163752.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163816_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163926_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_165713-(4).jpg</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>926611</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>4050</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="n">
+        <v>675784</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ТВГ-15М (51А)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-4.jpg</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>9268253</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="n">
+        <v>327189</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>КАМАЗ-5490 с полуприцепом НЕФАЗ-93341</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-16-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-15-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-13-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-3-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-11.jpg</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>9464798</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>5900</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="n">
+        <v>461812</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ТВГ-15М (51А) белый/зеленый автовышка</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-7.jpg</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>9514508</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>103436</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="n">
+        <v>557769</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Троллейбус ЗИУ-5 синий, маршрут №41 Москва</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112326_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112331.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112334_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112337_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112350.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1.jpg</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>9523751</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ЗиУ</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="n">
+        <v>156421</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Автобус ЗиЛ-158А экскурсионный</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-5.jpg</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>9533455</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="n">
+        <v>666531</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>КАМАЗ-43118 бортовой</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-7.jpg</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>9578983</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="n">
+        <v>176765</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ТЗ-200 (на шасси МАЗ-200), армейский</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-7.jpg</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>9733160</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>МАЗ</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="n">
+        <v>473810</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Икарус-250.70 Интурист земляничный</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162825_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162830_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162835_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162845.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163006_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163018_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163042.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163057_1.jpg</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>9840829</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>12300</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,25 +498,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>356447</v>
+        <v>484585</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>КАМАЗ-54901 с полуприцепом НЕФАЗ-93341</t>
+          <t>ЭО-3532 (5511)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/932-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/931-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/933-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/935-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/934-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/937.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/936.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/938.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/939.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145-10.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10001182</t>
+          <t>10000712</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5200</v>
+        <v>6250</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -525,7 +525,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -561,34 +561,34 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>707012</v>
+        <v>725366</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>КММ-2 (51)</t>
+          <t>КАМАЗ-65115 самосвал желтый</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-2.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-8.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10001183</t>
+          <t>10000940</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3250</v>
+        <v>6800</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -601,7 +601,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SSM1656</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>новый</t>
@@ -609,7 +613,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;img src="https://ritmonexx.ru/images/cache/additional/800x600/kamaz-65115-666976-5.jpg?54fc43e543c281fc5898076f12b0b2c0" alt="kamaz-65115-666976-5.jpg?54fc43e543c281fc5898076f12b0b2c0" /&gt;&lt;/p&gt;&lt;p&gt;&lt;img src="https://ritmonexx.ru/images/cache/additional/800x600/kamaz-65115-666976-8.jpg?14749c9c96ed9bb6482af2a8e8b5e44b" alt="kamaz-65115-666976-8.jpg?14749c9c96ed9bb6482af2a8e8b5e44b" /&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -624,34 +628,34 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>509635</v>
+        <v>356447</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>КО-829А (4333) поливалка</t>
+          <t>КАМАЗ-54901 с полуприцепом НЕФАЗ-93341</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/932-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/931-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/933-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/935-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/934-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/937.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/936.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/938.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/939.jpg</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10001581</t>
+          <t>10001182</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2250</v>
+        <v>5200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -687,34 +691,34 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>655982</v>
+        <v>707012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>КАМАЗ-6520 серый</t>
+          <t>КММ-2 (51)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-2.jpg</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10001778</t>
+          <t>10001183</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3300</v>
+        <v>3250</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -750,34 +754,34 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>507464</v>
+        <v>509635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Автобус Икарус-250.58 Интурбюро</t>
+          <t>КО-829А (4333) поливалка</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055945.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055951.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055955_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055959.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060002_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060008.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060019.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060133_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060150_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-8.jpg</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10001836</t>
+          <t>10001581</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10200</v>
+        <v>2250</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -813,34 +817,34 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>557768</v>
+        <v>655982</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Троллейбус ЗИУ-5 белый</t>
+          <t>КАМАЗ-6520 серый</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112604_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112614_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112611_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112608.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112630.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1-(2).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-8.jpg</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1062271</t>
+          <t>10001778</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7200</v>
+        <v>3300</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ЗиУ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -856,12 +860,12 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Новый</t>
+          <t>новый</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -876,34 +880,34 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>342834</v>
+        <v>507464</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Автобус ЛиАЗ-677М бело-желтый СОВА</t>
+          <t>Автобус Икарус-250.58 Интурбюро</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-6-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055945.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055951.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055955_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055959.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060002_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060008.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060019.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060133_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060150_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351-(1).jpg</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1149836</t>
+          <t>10001836</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3250</v>
+        <v>10200</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -919,12 +923,12 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Новый</t>
+          <t>новый</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>&lt;p&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -939,59 +943,47 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>483603</v>
+        <v>151979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KAMAZ-65801-T5 самосвал</t>
+          <t>Бокс SSM (19x8x8 см)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-6-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-7-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-8-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/sredniy-boks-ssm-19x8x8-sm-12270.jpg</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1159045</t>
+          <t>10001886</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7100</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>КамАЗ</t>
-        </is>
-      </c>
+        <v>690</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Start Scale Models (SSM)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>SSM1547</t>
-        </is>
-      </c>
+          <t>Пластмасса</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Новый</t>
+          <t>новый</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>&lt;p&gt;Бокс новый. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1006,34 +998,34 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>694057</v>
+        <v>557768</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ПУ-20 (51А)</t>
+          <t>Троллейбус ЗИУ-5 белый</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112604_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112614_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112611_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112608.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112630.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1-(2).jpg</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1314693</t>
+          <t>1062271</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2900</v>
+        <v>7200</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>ЗиУ</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1054,7 +1046,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1069,34 +1061,34 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>221707</v>
+        <v>342834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ГЗСА-3711 (53) Почтовый фургон</t>
+          <t>Автобус ЛиАЗ-677М бело-желтый СОВА</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/gtk-32-51-657585-5.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-6-(1).jpg</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1343751</t>
+          <t>1149836</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2800</v>
+        <v>3250</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>ЛиАЗ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1109,11 +1101,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>SSM1341</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -1121,7 +1109,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1136,34 +1124,34 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>414794</v>
+        <v>483603</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Контейнерный мусоровоз M-30 (53)</t>
+          <t>KAMAZ-65801-T5 самосвал</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-11.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-12.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-6-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-7-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-8-(1).jpg</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1388338</t>
+          <t>1159045</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6100</v>
+        <v>7100</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1176,7 +1164,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SSM1547</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -1184,7 +1176,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1199,34 +1191,34 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>501164</v>
+        <v>694057</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Автобус Икарус 255.70 антик</t>
+          <t>ПУ-20 (51А)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/1-50.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/2-39.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-6.jpg</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1440090</t>
+          <t>1314693</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7100</v>
+        <v>2900</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1247,7 +1239,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1262,34 +1254,34 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>588725</v>
+        <v>221707</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Автобус Икарус-238</t>
+          <t>ГЗСА-3711 (53) Почтовый фургон</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/nashi-avtobusy-50-laz-697n-turist-110378-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/gtk-32-51-657585-5.jpg</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1809086</t>
+          <t>1343751</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>10250</v>
+        <v>2800</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ModelPro</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1304,7 +1296,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0264MP</t>
+          <t>SSM1341</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1314,7 +1306,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1329,34 +1321,34 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>207965</v>
+        <v>414794</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>БЕЛАЗ-7522 (ранний) карьерный самосвал песочный</t>
+          <t>Контейнерный мусоровоз M-30 (53)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-653275-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-11.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-12.jpg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2066781</t>
+          <t>1388338</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5800</v>
+        <v>6100</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>БелАЗ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1369,11 +1361,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>SSM1313</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -1381,7 +1369,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1396,34 +1384,34 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>630928</v>
+        <v>501164</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KAMAZ-65225 жёлтый</t>
+          <t>Автобус Икарус 255.70 антик</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/1-50.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/2-39.jpg</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2075191</t>
+          <t>1440090</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5300</v>
+        <v>7100</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1444,7 +1432,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1459,39 +1447,51 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>159743</v>
+        <v>588725</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Большой бокс SSM (32x10.5x10.5 см)</t>
+          <t>Автобус Икарус-238</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/bolshoy-boks-ssm-32x105x105-sm-14917-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/nashi-avtobusy-50-laz-697n-turist-110378-6.jpg</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2342651</t>
+          <t>1809086</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
+        <v>10250</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>ModelPro</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Пластмасса</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0264MP</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Бокс новыйСамовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1514,34 +1514,34 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>636031</v>
+        <v>207965</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>СБ-92 (5511) серый бетоносмеситель</t>
+          <t>БЕЛАЗ-7522 (ранний) карьерный самосвал песочный</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-653275-8.jpg</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2362962</t>
+          <t>2066781</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4800</v>
+        <v>5800</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>БелАЗ</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1554,7 +1554,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SSM1313</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -1577,29 +1581,29 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>214442</v>
+        <v>630928</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>КРАЗ-214 Мосгортранс</t>
+          <t>KAMAZ-65225 жёлтый</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/241-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/242-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/243-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/244-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/248.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-8.jpg</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2428141</t>
+          <t>2075191</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2750</v>
+        <v>5300</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>КрАЗ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1625,7 +1629,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1640,44 +1644,36 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>472680</v>
+        <v>159743</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Автобус Икарус 55.14 Ставрополь</t>
+          <t>Большой бокс SSM (32x10.5x10.5 см)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135027_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135038.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135049_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135057_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135107_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135117_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135129.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135143_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135202.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135309_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135323_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135345_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/bolshoy-boks-ssm-32x105x105-sm-14917-(1).jpg</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2532465</t>
+          <t>2342651</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>6300</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Ikarus</t>
-        </is>
-      </c>
+        <v>1250</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Металл/пластмасса</t>
+          <t>Пластмасса</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1688,7 +1684,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Бокс новыйСамовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1703,34 +1699,34 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>655467</v>
+        <v>636031</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Трамвай Tatra-T3SU синий</t>
+          <t>СБ-92 (5511) серый бетоносмеситель</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-5.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-6.jpg</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2582990</t>
+          <t>2362962</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>7300</v>
+        <v>4800</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1766,34 +1762,34 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>557767</v>
+        <v>214442</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Троллейбус ЗИУ-5 красный</t>
+          <t>КРАЗ-214 Мосгортранс</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112433.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112444_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112437_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112441_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112455_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/241-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/242-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/243-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/244-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/248.jpg</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2624588</t>
+          <t>2428141</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>7200</v>
+        <v>2750</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ЗиУ</t>
+          <t>КрАЗ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1814,7 +1810,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1829,34 +1825,34 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>488956</v>
+        <v>472680</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Троллейбус ТГ-3</t>
+          <t>Автобус Икарус 55.14 Ставрополь</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-6-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-2.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135027_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135038.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135049_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135057_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135107_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135117_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135129.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135143_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135202.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135309_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135323_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135345_1.jpg</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2771714</t>
+          <t>2532465</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2850</v>
+        <v>6300</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ТГ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1877,7 +1873,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1892,29 +1888,29 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>223983</v>
+        <v>655467</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>МАЗ-5550 Мосметро</t>
+          <t>Трамвай Tatra-T3SU синий</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-6-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-10-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-8-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-9-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-16.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-3-1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-5.jpg</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3096000</t>
+          <t>2582990</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3800</v>
+        <v>7300</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>МАЗ</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1922,7 +1918,11 @@
           <t>Start Scale Models (SSM)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Металл/пластмасса</t>
@@ -1951,34 +1951,34 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>464451</v>
+        <v>557767</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ПР-53 (52)</t>
+          <t>Троллейбус ЗИУ-5 красный</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112433.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112444_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112437_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112441_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112455_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1-(1).jpg</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3114877</t>
+          <t>2624588</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2850</v>
+        <v>7200</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>ЗиУ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2014,34 +2014,34 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>441039</v>
+        <v>488956</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Пескоразбрасыватель ПР-53 (52)</t>
+          <t>Троллейбус ТГ-3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/213-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/211-(3).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/212-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/214-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/215-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/216-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-6-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-2.jpg</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3161825</t>
+          <t>2771714</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4450</v>
+        <v>2850</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>ТГ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2077,29 +2077,29 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>6463</v>
+        <v>223983</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Тигр 233001 пикап песочный</t>
+          <t>МАЗ-5550 Мосметро</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/233001-pikap-11486-1-1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-6-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-10-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-8-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-9-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-16.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/maz-5550-samosval-metro-66725-3-1.jpg</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3163203</t>
+          <t>3096000</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1650</v>
+        <v>3800</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>МАЗ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2107,11 +2107,7 @@
           <t>Start Scale Models (SSM)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Металл/пластмасса</t>
@@ -2140,34 +2136,34 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>189569</v>
+        <v>464451</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>КАвЗ-3976 (бело-голубой)</t>
+          <t>ПР-53 (52)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pr-53-52-112931-6.jpg</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>321488</t>
+          <t>3114877</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5600</v>
+        <v>2850</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>КАвЗ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2180,11 +2176,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>SSM4017</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -2192,7 +2184,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2207,34 +2199,34 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>621961</v>
+        <v>441039</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>АКПМ-3 (130)</t>
+          <t>Пескоразбрасыватель ПР-53 (52)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/213-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/211-(3).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/212-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/214-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/215-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/216-(1).jpg</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3229352</t>
+          <t>3161825</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2800</v>
+        <v>4450</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2255,7 +2247,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2270,34 +2262,34 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>483604</v>
+        <v>6463</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Автобус Икарус-280 красный</t>
+          <t>Тигр 233001 пикап песочный</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/233001-pikap-11486-1-1.jpg</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3342857</t>
+          <t>3163203</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5300</v>
+        <v>1650</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2310,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2333,29 +2325,29 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>280346</v>
+        <v>189569</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ЗИЛ-ММЗ-585Л самосвал</t>
+          <t>КАвЗ-3976 (бело-голубой)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-13.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-14.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240.jpg</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3430175</t>
+          <t>321488</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6800</v>
+        <v>5600</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ММЗ</t>
+          <t>КАвЗ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2368,8 +2360,16 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>SSM4017</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -2392,34 +2392,34 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>457283</v>
+        <v>621961</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>КАМАЗ-65951 самосвал</t>
+          <t>АКПМ-3 (130)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-6.jpg</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3466651</t>
+          <t>3229352</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6800</v>
+        <v>2800</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2432,11 +2432,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>SSM1533</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -2459,34 +2455,34 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>518058</v>
+        <v>483604</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>БЕЦЕМА АЦ/АТЗ (KAMAZ-65207-87)</t>
+          <t>Автобус Икарус-280 красный</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-6.jpg</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3563754</t>
+          <t>3342857</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4250</v>
+        <v>5300</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2507,7 +2503,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2522,34 +2518,34 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>500143</v>
+        <v>280346</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Автобус Икарус 255.70 красный</t>
+          <t>ЗИЛ-ММЗ-585Л самосвал</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160531_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160540.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160536-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160543_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160547_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160554_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160652_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160710.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160731_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160744.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-13.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-14.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-9.jpg</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3785921</t>
+          <t>3430175</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>7200</v>
+        <v>6800</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>ММЗ</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2557,11 +2553,7 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
@@ -2570,7 +2562,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2585,34 +2577,34 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>460540</v>
+        <v>457283</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Автобус Икарус-260.06</t>
+          <t>КАМАЗ-65951 самосвал</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-7.jpg</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4069148</t>
+          <t>3466651</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3100</v>
+        <v>6800</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2625,7 +2617,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>SSM1533</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -2633,7 +2629,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2648,34 +2644,34 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>441302</v>
+        <v>518058</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Автобус Икарус 256.54 скарлат</t>
+          <t>БЕЦЕМА АЦ/АТЗ (KAMAZ-65207-87)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122158.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122209.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122223_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122220_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122213_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122217_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122229.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122237.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122401.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122422_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-9.jpg</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4097841</t>
+          <t>3563754</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>15300</v>
+        <v>4250</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2696,7 +2692,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2711,34 +2707,34 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>291330</v>
+        <v>500143</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Skoda 706 MTTN с полуприцепом Alka N12CH Schlossberg Sekt</t>
+          <t>Автобус Икарус 255.70 красный</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160531_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160540.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160536-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160543_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160547_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160554_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160652_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160710.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160731_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240821_160744.jpg</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4178680</t>
+          <t>3785921</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>7800</v>
+        <v>7200</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Škoda</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2759,7 +2755,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2774,25 +2770,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>507463</v>
+        <v>460540</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Автобус Икарус-250.58 белый</t>
+          <t>Автобус Икарус-260.06</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055133.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055138.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055143.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055146_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055151.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055156_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055204_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055312_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055329_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-6.jpg</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>419962</t>
+          <t>4069148</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>10300</v>
+        <v>3100</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2801,7 +2797,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2822,7 +2818,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2837,34 +2833,34 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>199553</v>
+        <v>441302</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>КАЗ-ММЗ-4502 самосвал</t>
+          <t>Автобус Икарус 256.54 скарлат</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-15.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-16.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122158.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122209.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122223_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122220_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122213_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122217_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122229.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122237.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122401.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122422_1.jpg</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4250260</t>
+          <t>4097841</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2600</v>
+        <v>15300</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ММЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2877,11 +2873,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>SSM1293</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -2904,29 +2896,29 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>584696</v>
+        <v>291330</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>КАМАЗ-6520 рестайлинг самосвал</t>
+          <t>Skoda 706 MTTN с полуприцепом Alka N12CH Schlossberg Sekt</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-7-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-8-1-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-9.jpg</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4256288</t>
+          <t>4178680</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>8300</v>
+        <v>7800</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Škoda</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2967,34 +2959,34 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>326092</v>
+        <v>507463</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>КАМАЗ-54901 с п/п НЕФАЗ-93341 белый</t>
+          <t>Автобус Икарус-250.58 белый</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/902-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/901-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/904.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/903-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/905.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/907.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/906.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055133.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055138.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055143.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055146_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055151.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055156_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055204_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055312_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055329_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351.jpg</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4381093</t>
+          <t>419962</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>6800</v>
+        <v>10300</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3015,7 +3007,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3030,34 +3022,34 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>326092</v>
+        <v>199553</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>КАМАЗ-54901 с полуприцепом НЕФАЗ-93341</t>
+          <t>КАЗ-ММЗ-4502 самосвал</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-11.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-15.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-16.jpg</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4386018</t>
+          <t>4250260</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>5900</v>
+        <v>2600</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>ММЗ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3070,7 +3062,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>SSM1293</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3093,29 +3089,29 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>722938</v>
+        <v>584696</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Volvo F12 с полуприцепом Fruehauf Savoyarde белая/синяя</t>
+          <t>КАМАЗ-6520 рестайлинг самосвал</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f89-s-polupricepom-fruehauf-savoyarde-117743-3.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-7-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-8-1-(1).jpg</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4386166</t>
+          <t>4256288</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>8250</v>
+        <v>8300</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Volvo</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3133,11 +3129,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>SSM7077</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3145,7 +3137,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3160,34 +3152,34 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>696912</v>
+        <v>326092</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Икарус 222 светло зеленый</t>
+          <t>КАМАЗ-54901 с п/п НЕФАЗ-93341 белый</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-5.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/902-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/901-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/904.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/903-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/905.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/907.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/906.jpg</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4775954</t>
+          <t>4381093</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>10250</v>
+        <v>6800</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>ModelPro</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3197,7 +3189,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Смола</t>
+          <t>Металл/пластмасса</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3208,7 +3200,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3223,25 +3215,25 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>654956</v>
+        <v>326092</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KAMAZ-65225 (рестайлинг)</t>
+          <t>КАМАЗ-54901 с полуприцепом НЕФАЗ-93341</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-11.jpg</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4849168</t>
+          <t>4386018</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3300</v>
+        <v>5900</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3271,7 +3263,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3286,29 +3278,29 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>198946</v>
+        <v>722938</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>КРАЗ-257Б1 контейнер</t>
+          <t>Volvo F12 с полуприцепом Fruehauf Savoyarde белая/синяя</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-10.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f89-s-polupricepom-fruehauf-savoyarde-117743-3.jpg</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4910920</t>
+          <t>4386166</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3800</v>
+        <v>8250</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>КрАЗ</t>
+          <t>Volvo</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3328,7 +3320,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>SSM4017</t>
+          <t>SSM7077</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3338,7 +3330,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3353,34 +3345,34 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>633016</v>
+        <v>696912</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>КАМАЗ-5511 самосвал темно-зеленый</t>
+          <t>Икарус 222 светло зеленый</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-5.jpg</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4912801</t>
+          <t>4775954</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>6200</v>
+        <v>10250</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>ModelPro</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3388,7 +3380,11 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Смола</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
@@ -3397,7 +3393,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3412,34 +3408,34 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>486148</v>
+        <v>654956</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>АК-75В (130)</t>
+          <t>KAMAZ-65225 (рестайлинг)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-2-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-7-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-8-3.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294.jpg</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4986574</t>
+          <t>4849168</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>6250</v>
+        <v>3300</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3452,11 +3448,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>SSM1549</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3464,7 +3456,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3479,34 +3471,34 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>472677</v>
+        <v>198946</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>КАвЗ-651 рапсодия</t>
+          <t>КРАЗ-257Б1 контейнер</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/5-18.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/2-23.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/4-19.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/3-20.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/1-30.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-10.jpg</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>5014580</t>
+          <t>4910920</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3250</v>
+        <v>3800</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>КАвЗ</t>
+          <t>КрАЗ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3519,7 +3511,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>SSM4017</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3527,7 +3523,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3542,21 +3538,21 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>707012</v>
+        <v>633016</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>КММ-2 (51)</t>
+          <t>КАМАЗ-5511 самосвал темно-зеленый</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-6.jpg</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>5048762</t>
+          <t>4912801</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -3564,12 +3560,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3577,16 +3573,8 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Бачки</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3594,7 +3582,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3609,34 +3597,34 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>477641</v>
+        <v>486148</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ikarus-280.64 оранжевый</t>
+          <t>АК-75В (130)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-2-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-7-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-8-3.jpg</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5054284</t>
+          <t>4986574</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>5800</v>
+        <v>6250</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3649,7 +3637,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>SSM1549</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3672,34 +3664,34 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>588726</v>
+        <v>472677</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>КАМАЗ-6522 рестайлинг желтый</t>
+          <t>КАвЗ-651 рапсодия</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/5-18.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/2-23.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/4-19.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/3-20.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/1-30.jpg</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>5085617</t>
+          <t>5014580</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>6800</v>
+        <v>3250</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>КАвЗ</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3720,7 +3712,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3735,29 +3727,29 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>153285</v>
+        <v>707012</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ЗИС-151 бортовой темно зеленый</t>
+          <t>КММ-2 (51)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-9.jpg</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5172843</t>
+          <t>5048762</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2450</v>
+        <v>6200</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>ЗиС</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3775,7 +3767,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Бачки</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3798,34 +3794,34 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>459312</v>
+        <v>477641</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ЗИЛ-4333 KО-829А поливалка</t>
+          <t>Ikarus-280.64 оранжевый</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-10.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-6.jpg</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>5294623</t>
+          <t>5054284</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>5250</v>
+        <v>5800</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3861,34 +3857,34 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>499998</v>
+        <v>588726</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>МКМ-2 (4333)</t>
+          <t>КАМАЗ-6522 рестайлинг желтый</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-6-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-7-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-7.jpg</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>5463365</t>
+          <t>5085617</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2250</v>
+        <v>6800</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3909,7 +3905,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -3924,29 +3920,29 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>470904</v>
+        <v>153285</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tatra-815S3 самосвал оранжевый/синий</t>
+          <t>ЗИС-151 бортовой темно зеленый</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zis-151-bortovoy-12308-9.jpg</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5711242</t>
+          <t>5172843</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>6250</v>
+        <v>2450</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>ЗиС</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3964,11 +3960,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>SSM1538</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3976,7 +3968,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -3991,34 +3983,34 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>488484</v>
+        <v>459312</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Бокс 32 см (32х9х9) DEMPRICE с винтами</t>
+          <t>ЗИЛ-4333 KО-829А поливалка</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101849.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-10.jpg</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6122001</t>
+          <t>5294623</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1250</v>
+        <v>5250</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4028,7 +4020,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Пластмасса</t>
+          <t>Металл/пластмасса</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -4039,7 +4031,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Бокс новый.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4054,25 +4046,25 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>150038</v>
+        <v>499998</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ЗИЛ-130-76 бортовой (поздняя облицовка радиатора)</t>
+          <t>МКМ-2 (4333)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-6-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkm-2-4333-112722-7-(1).jpg</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6217765</t>
+          <t>5463365</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2450</v>
+        <v>2250</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -4081,7 +4073,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4094,11 +4086,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>SSM1003</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4121,29 +4109,29 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>487535</v>
+        <v>470904</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KAMAЗ-43253 Рестайлинг</t>
+          <t>Tatra-815S3 самосвал оранжевый/синий</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-8.jpg</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>6249403</t>
+          <t>5711242</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>5650</v>
+        <v>6250</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4161,7 +4149,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>SSM1538</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4169,7 +4161,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4184,34 +4176,34 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>640208</v>
+        <v>488484</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>КАМАЗ-43118 рестайлинг</t>
+          <t>Бокс 32 см (32х9х9) DEMPRICE с винтами</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101849.jpg</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>639065</t>
+          <t>6122001</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>4900</v>
+        <v>1250</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4221,7 +4213,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Металл/пластмасса</t>
+          <t>Пластмасса</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4232,7 +4224,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Бокс новый.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4247,34 +4239,34 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>641239</v>
+        <v>150038</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>КАМАЗ-6520 Рестайлинг зеленый</t>
+          <t>ЗИЛ-130-76 бортовой (поздняя облицовка радиатора)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-76-bortovoy-pozdnyaya-oblicovka-radiatora-12050-6.jpg</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>6440694</t>
+          <t>6217765</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3300</v>
+        <v>2450</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4287,7 +4279,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>SSM1003</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4295,7 +4291,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4310,34 +4306,34 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>473852</v>
+        <v>487535</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Икарус 250.70 Чили ИНТУРИСТ DEMPRICE</t>
+          <t>KAMAЗ-43253 Рестайлинг</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184241_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184254_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184312_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184333_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184354_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184415.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184450_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184950_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184840_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_185157_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-8.jpg</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>6455073</t>
+          <t>6249403</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>15300</v>
+        <v>5650</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4358,7 +4354,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4373,34 +4369,34 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>342832</v>
+        <v>640208</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Автобус ЛиАЗ-677М бело-синий СОВА</t>
+          <t>КАМАЗ-43118 рестайлинг</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-6-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-8.jpg</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>6498567</t>
+          <t>639065</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3250</v>
+        <v>4900</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4421,7 +4417,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4436,34 +4432,34 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>334587</v>
+        <v>641239</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Прицеп МАЗ-8926</t>
+          <t>КАМАЗ-6520 Рестайлинг зеленый</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-655292-8.jpg</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6762234</t>
+          <t>6440694</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2250</v>
+        <v>3300</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>МАЗ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4499,21 +4495,21 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>474035</v>
+        <v>473852</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Икарус 250.70 клубничный ИНТУРИСТ</t>
+          <t>Икарус 250.70 Чили ИНТУРИСТ DEMPRICE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173347.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173351_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173403.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173413.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173417_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173528.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173603_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173612.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184241_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184254_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184312_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184333_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184354_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184415.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184450_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184950_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184840_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_185157_1.jpg</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>6773621</t>
+          <t>6455073</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -4562,34 +4558,34 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>519214</v>
+        <v>342832</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>KAMAZ-6520-21010-53 самосвал</t>
+          <t>Автобус ЛиАЗ-677М бело-синий СОВА</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-6-(1).jpg</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>7206133</t>
+          <t>6498567</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>4250</v>
+        <v>3250</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>ЛиАЗ</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4610,7 +4606,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4625,34 +4621,34 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>205299</v>
+        <v>334587</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>КрАЗ-6322 БРО-200</t>
+          <t>Прицеп МАЗ-8926</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-11.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-7.jpg</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>7250974</t>
+          <t>6762234</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2050</v>
+        <v>2250</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>КрАЗ</t>
+          <t>МАЗ</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Наш Автопром</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4665,11 +4661,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Н947</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4692,21 +4684,21 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>507465</v>
+        <v>474035</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Автобус Икарус-250.58 Совтрансавто</t>
+          <t>Икарус 250.70 клубничный ИНТУРИСТ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060555.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060600_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060606_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060611.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060615.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060619_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060627_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060740_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060800.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351-(2).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173347.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173351_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173403.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173413.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173417_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173528.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173603_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173612.jpg</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>7322725</t>
+          <t>6773621</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -4740,7 +4732,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -4755,25 +4747,25 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>564883</v>
+        <v>519214</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KAMAZ-65952 самосвал</t>
+          <t>KAMAZ-6520-21010-53 самосвал</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-9.jpg</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>7408909</t>
+          <t>7206133</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>4200</v>
+        <v>4250</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4782,7 +4774,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4818,34 +4810,34 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>7575</v>
+        <v>205299</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ЗИЛ-130 бортовой (ранняя облицовка радиатора)</t>
+          <t>КрАЗ-6322 БРО-200</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-11.jpg</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>7424562</t>
+          <t>7250974</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2400</v>
+        <v>2050</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>КрАЗ</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Наш Автопром</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4858,7 +4850,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Н947</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4866,7 +4862,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -4881,25 +4877,25 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>499198</v>
+        <v>507465</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Икарус-280 белый с красной полосой</t>
+          <t>Автобус Икарус-250.58 Совтрансавто</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060555.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060600_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060606_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060611.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060615.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060619_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060627_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060740_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060800.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351-(2).jpg</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>7438713</t>
+          <t>7322725</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>5800</v>
+        <v>15300</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4908,7 +4904,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4929,7 +4925,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -4944,34 +4940,34 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>460537</v>
+        <v>564883</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ЗИЛ-4333 КО-829А пескоразбрасыватель</t>
+          <t>KAMAZ-65952 самосвал</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-7.jpg</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>745858</t>
+          <t>7408909</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>4900</v>
+        <v>4200</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4984,11 +4980,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>SSM1520</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4996,7 +4988,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5011,34 +5003,34 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>519215</v>
+        <v>7575</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KAMAZ-65207-87 (S5) бортовой</t>
+          <t>ЗИЛ-130 бортовой (ранняя облицовка радиатора)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-130-bortovoy-rannyaya-oblicovka-radiatora-11768-6.jpg</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>7494811</t>
+          <t>7424562</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>4900</v>
+        <v>2400</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5059,7 +5051,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5074,34 +5066,34 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>693380</v>
+        <v>499198</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Volvo F12 с полуприцепом Lamberet</t>
+          <t>Икарус-280 белый с красной полосой</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-10.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-6.jpg</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>7567444</t>
+          <t>7438713</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>12800</v>
+        <v>5800</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Volvo</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5122,7 +5114,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5137,29 +5129,29 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>177912</v>
+        <v>460537</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Полуприцеп МАЗ-5215 зелёный</t>
+          <t>ЗИЛ-4333 КО-829А пескоразбрасыватель</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-4-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-peskorazbrasyvatel-113839-7.jpg</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>7640294</t>
+          <t>745858</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1750</v>
+        <v>4900</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>МАЗ</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5179,7 +5171,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>SSM7011</t>
+          <t>SSM1520</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5189,7 +5181,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5204,34 +5196,34 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>183350</v>
+        <v>519215</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ЯАЗ-205 самосвал зеленый</t>
+          <t>KAMAZ-65207-87 (S5) бортовой</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-14.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-8.jpg</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>7644570</t>
+          <t>7494811</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2700</v>
+        <v>4900</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ЯАЗ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5252,7 +5244,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5267,34 +5259,34 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>474047</v>
+        <v>693380</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Автобус Икарус 280.33 г. Орёл</t>
+          <t>Volvo F12 с полуприцепом Lamberet</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141310.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141318_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141322.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141330_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141335_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141340.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141352_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141456.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141651.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141816.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/volvo-f12-s-polupricepom-lamberet-666124-10.jpg</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>7680062</t>
+          <t>7567444</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>15300</v>
+        <v>12800</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>Volvo</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5302,7 +5294,11 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
@@ -5311,7 +5307,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5326,29 +5322,29 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>477068</v>
+        <v>177912</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>КамАЗ-65802-87 (S5)</t>
+          <t>Полуприцеп МАЗ-5215 зелёный</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-9-1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-4-(1).jpg</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>7722142</t>
+          <t>7640294</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>7150</v>
+        <v>1750</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>МАЗ</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5368,7 +5364,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>SSM1546</t>
+          <t>SSM7011</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5378,7 +5374,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5393,34 +5389,34 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>657404</v>
+        <v>183350</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>КамАЗ-6522 оранжевый</t>
+          <t>ЯАЗ-205 самосвал зеленый</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/yaaz-205-samosval-zelenyy-26400-14.jpg</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>785738</t>
+          <t>7644570</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>4250</v>
+        <v>2700</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>ЯАЗ</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5441,7 +5437,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5456,34 +5452,34 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>441961</v>
+        <v>474047</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Мусоровоз КО-413 (53) SSM</t>
+          <t>Автобус Икарус 280.33 г. Орёл</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/d5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141310.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141318_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141322.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141330_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141335_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141340.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141352_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141456.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141651.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141816.jpg</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>7902021</t>
+          <t>7680062</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>4650</v>
+        <v>15300</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5491,11 +5487,7 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
@@ -5519,34 +5511,34 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>495095</v>
+        <v>477068</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PETERBILT 350</t>
+          <t>КамАЗ-65802-87 (S5)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250313_142201.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-9-1.jpg</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>8339384</t>
+          <t>7722142</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>4150</v>
+        <v>7150</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Peterbilt</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>IXO грузовики (серии TRU)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5554,8 +5546,16 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>SSM1546</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -5578,34 +5578,34 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>630206</v>
+        <v>657404</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Norba KI-12 (5334) мусоровоз</t>
+          <t>КамАЗ-6522 оранжевый</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-8.jpg</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>8843536</t>
+          <t>785738</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>6250</v>
+        <v>4250</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>МАЗ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5641,34 +5641,34 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>364917</v>
+        <v>441961</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>КАМАЗ-65206 с полуприцепом НЕФАЗ-93341</t>
+          <t>Мусоровоз КО-413 (53) SSM</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/954.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/952.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/951.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/953.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/955.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/956.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/957.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/958.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/959.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/d5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d9.jpg</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>8845471</t>
+          <t>7902021</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>7900</v>
+        <v>4650</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5681,11 +5681,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>102972</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5708,34 +5704,34 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>472681</v>
+        <v>495095</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Автобус ЛАЗ-695Н бело-красный</t>
+          <t>PETERBILT 350</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111725.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111705_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111702.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111708_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111711_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111220_1-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250313_142201.jpg</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>8879921</t>
+          <t>8339384</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>5800</v>
+        <v>4150</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ЛАЗ</t>
+          <t>Peterbilt</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>IXO грузовики (серии TRU)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5743,11 +5739,7 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
@@ -5771,29 +5763,29 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>472729</v>
+        <v>630206</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tatra 815 V26 бортовая с тентом</t>
+          <t>Norba KI-12 (5334) мусоровоз</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0021.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0023.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0022.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0024.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0025.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0026.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-8.jpg</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>8914544</t>
+          <t>8843536</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>5750</v>
+        <v>6250</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>МАЗ</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5819,7 +5811,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -5834,34 +5826,34 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>469263</v>
+        <v>364917</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tatra-815S1 самосвал красный</t>
+          <t>КАМАЗ-65206 с полуприцепом НЕФАЗ-93341</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/954.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/952.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/951.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/953.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/955.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/956.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/957.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/958.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/959.jpg</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>9007302</t>
+          <t>8845471</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>5750</v>
+        <v>7900</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5876,7 +5868,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>SSM1537</t>
+          <t>102972</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5901,34 +5893,34 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>214234</v>
+        <v>472681</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ГЗСА-893А (52) Мебельный фургон</t>
+          <t>Автобус ЛАЗ-695Н бело-красный</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-12-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-13-1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111725.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111705_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111702.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111708_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111711_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111220_1-(1).jpg</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>9039863</t>
+          <t>8879921</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2750</v>
+        <v>5800</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>ЛАЗ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5941,11 +5933,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>SSM1330</t>
-        </is>
-      </c>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5968,34 +5956,34 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>491552</v>
+        <v>472729</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Троллейбус Skoda-9TR</t>
+          <t>Tatra 815 V26 бортовая с тентом</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0021.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0023.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0022.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0024.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0025.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0026.jpg</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>9103969</t>
+          <t>8914544</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3050</v>
+        <v>5750</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Škoda</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6016,7 +6004,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6031,34 +6019,34 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>516931</v>
+        <v>469263</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>КамАЗ-65802-87 (S5) самосвал</t>
+          <t>Tatra-815S1 самосвал красный</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-9-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-10-1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-9.jpg</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>9158455</t>
+          <t>9007302</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>5250</v>
+        <v>5750</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6071,7 +6059,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>SSM1537</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -6079,7 +6071,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6094,34 +6086,34 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>695471</v>
+        <v>214234</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Полуприцеп НАМИ-790</t>
+          <t>ГЗСА-893А (52) Мебельный фургон</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-2.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-12-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/gzsa-893a-52-mebelnyy-furgon-64701-13-1.jpg</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>9199667</t>
+          <t>9039863</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3750</v>
+        <v>2750</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>НАМИ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6134,7 +6126,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>SSM1330</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -6157,34 +6153,34 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>473509</v>
+        <v>491552</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Автобус Икарус 256.54 Киноварь</t>
+          <t>Троллейбус Skoda-9TR</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191021_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191025_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191029.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191032_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191036.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191048_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191107_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191147_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191207_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-6.jpg</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>92437</t>
+          <t>9103969</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>9300</v>
+        <v>3050</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>Škoda</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6205,7 +6201,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6220,34 +6216,34 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>473515</v>
+        <v>516931</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ЛиАЗ-5256 турмалин желто-белый</t>
+          <t>КамАЗ-65802-87 (S5) самосвал</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163716.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163720_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163746.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163741_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163752.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163816_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163926_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_165713-(4).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-9-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-10-1.jpg</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>926611</t>
+          <t>9158455</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>4050</v>
+        <v>5250</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6268,7 +6264,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6283,34 +6279,34 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>675784</v>
+        <v>695471</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ТВГ-15М (51А)</t>
+          <t>Полуприцеп НАМИ-790</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-4.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-2.jpg</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>9268253</t>
+          <t>9199667</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>5800</v>
+        <v>3750</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>НАМИ</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6346,34 +6342,34 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>327189</v>
+        <v>473509</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>КАМАЗ-5490 с полуприцепом НЕФАЗ-93341</t>
+          <t>Автобус Икарус 256.54 Киноварь</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-16-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-15-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-13-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-3-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-11.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191021_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191025_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191029.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191032_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191036.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191048_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191107_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191147_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191207_1.jpg</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>9464798</t>
+          <t>92437</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>5900</v>
+        <v>9300</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6409,34 +6405,34 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>461812</v>
+        <v>473515</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ТВГ-15М (51А) белый/зеленый автовышка</t>
+          <t>ЛиАЗ-5256 турмалин желто-белый</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163716.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163720_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163746.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163741_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163752.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163816_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_163926_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230927_165713-(4).jpg</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>9514508</t>
+          <t>926611</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3000</v>
+        <v>4050</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>ЛиАЗ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6449,11 +6445,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>103436</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -6461,7 +6453,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -6476,34 +6468,34 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>557769</v>
+        <v>675784</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Троллейбус ЗИУ-5 синий, маршрут №41 Москва</t>
+          <t>ТВГ-15М (51А)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112326_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112331.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112334_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112337_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112350.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-4.jpg</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>9523751</t>
+          <t>9268253</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>7200</v>
+        <v>5800</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>ЗиУ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6524,7 +6516,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -6539,34 +6531,34 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>156421</v>
+        <v>327189</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Автобус ЗиЛ-158А экскурсионный</t>
+          <t>КАМАЗ-5490 с полуприцепом НЕФАЗ-93341</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-5.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-16-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-15-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-13-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-3-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5490-s-polupricepom-nefaz-93341-iteco-86748-11.jpg</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>9533455</t>
+          <t>9464798</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1850</v>
+        <v>5900</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6587,7 +6579,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -6602,34 +6594,34 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>666531</v>
+        <v>461812</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>КАМАЗ-43118 бортовой</t>
+          <t>ТВГ-15М (51А) белый/зеленый автовышка</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15-52-112932-7.jpg</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>9578983</t>
+          <t>9514508</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3800</v>
+        <v>3000</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6642,7 +6634,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>103436</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -6650,7 +6646,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -6665,34 +6661,34 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>176765</v>
+        <v>557769</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ТЗ-200 (на шасси МАЗ-200), армейский</t>
+          <t>Троллейбус ЗИУ-5 синий, маршрут №41 Москва</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112326_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112331.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112334_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112337_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112350.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1.jpg</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>9733160</t>
+          <t>9523751</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2500</v>
+        <v>7200</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>МАЗ</t>
+          <t>ЗиУ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6713,7 +6709,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -6728,34 +6724,34 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>473810</v>
+        <v>156421</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Икарус-250.70 Интурист земляничный</t>
+          <t>Автобус ЗиЛ-158А экскурсионный</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162825_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162830_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162835_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162845.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163006_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163018_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163042.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163057_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-5.jpg</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>9840829</t>
+          <t>9533455</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>12300</v>
+        <v>1850</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6776,15 +6772,204 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="n">
+        <v>666531</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>КАМАЗ-43118 бортовой</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-7.jpg</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>9578983</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="n">
+        <v>176765</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ТЗ-200 (на шасси МАЗ-200), армейский</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tz200-na-shassi-maz200-armeyskiy-71-7.jpg</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>9733160</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>МАЗ</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="n">
+        <v>473810</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Икарус-250.70 Интурист земляничный</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162825_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162830_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162835_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162845.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163006_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163018_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163042.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163057_1.jpg</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>9840829</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>12300</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
           <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>г Химки, кв-л Клязьма</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -413,9 +413,5993 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID UNOMAG</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Фото (ссылки)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Лот №</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Единая цена</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Масштаб</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Артикул</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Состояние</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Местоположение</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Наличие</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>210771</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Пожарная вахта Горький-66</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/listing_media/bf/8f/ca/1e/a5/70/af/96/f4/90/5e/a9/e9/ac/97/1e/large.webp;https://scalebay.ru/static/listing_media/1e/87/c1/2d/f9/cb/42/c4/3f/6e/87/3b/69/0a/91/20/large.webp;https://scalebay.ru/static/listing_media/31/25/46/e5/2b/60/52/49/67/f7/45/20/7a/f1/87/d6/large.webp;https://scalebay.ru/static/listing_media/14/45/3f/8f/c1/b0/56/83/8d/7e/cf/1f/fc/1a/09/70/large.webp;https://scalebay.ru/static/listing_media/db/c6/ad/3c/9f/ef/4e/4e/fd/f4/57/88/9a/ca/1c/de/large.webp;https://scalebay.ru/static/listing_media/fc/d2/a3/1e/6d/ef/d9/9a/d0/31/c4/9d/f1/11/90/40/large.webp;https://scalebay.ru/static/listing_media/16/43/61/16/0c/17/a0/6f/18/fa/97/c6/a6/68/bc/05/large.webp</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>10000535</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Модель новая. 
+Самовывоз возможен только в г. Химки (Набережный проезд 3).
+Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. 
+Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>732630</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz NG 2232 с п/п Lamberet</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/mercedes-benz-ng-2232-s-p-p-lamberet-666120-10-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mercedes-benz-ng-2232-s-p-p-lamberet-666120.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mercedes-benz-ng-2232-s-p-p-lamberet-666120-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mercedes-benz-ng-2232-s-p-p-lamberet-666120-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mercedes-benz-ng-2232-s-p-p-lamberet-666120-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mercedes-benz-ng-2232-s-p-p-lamberet-666120-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mercedes-benz-ng-2232-s-p-p-lamberet-666120-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mercedes-benz-ng-2232-s-p-p-lamberet-666120-9.jpg</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10000644</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>8250</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>484585</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ЭО-3532 (5511)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/eo-3532-5511-115145-10.jpg</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>10000712</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6250</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>725366</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>КАМАЗ-65115 самосвал желтый</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-8.jpg</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10000940</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SSM1656</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;img src="https://ritmonexx.ru/images/cache/additional/800x600/kamaz-65115-666976-5.jpg?54fc43e543c281fc5898076f12b0b2c0" alt="kamaz-65115-666976-5.jpg?54fc43e543c281fc5898076f12b0b2c0" /&gt;&lt;/p&gt;&lt;p&gt;&lt;img src="https://ritmonexx.ru/images/cache/additional/800x600/kamaz-65115-666976-8.jpg?14749c9c96ed9bb6482af2a8e8b5e44b" alt="kamaz-65115-666976-8.jpg?14749c9c96ed9bb6482af2a8e8b5e44b" /&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>356447</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>КАМАЗ-54901 с полуприцепом НЕФАЗ-93341</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/932-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/931-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/933-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/935-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/934-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/937.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/936.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/938.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/939.jpg</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10001182</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>707012</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>КММ-2 (51)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-2.jpg</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10001183</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>509635</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>КО-829А (4333) поливалка</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-8.jpg</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10001581</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>507464</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Автобус Икарус-250.58 Интурбюро</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055945.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055951.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055955_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055959.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060002_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060008.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060019.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060133_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060150_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10001836</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>10200</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>151979</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Бокс SSM (19x8x8 см)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/sredniy-boks-ssm-19x8x8-sm-12270.jpg</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>10001886</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>690</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Пластмасса</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Бокс новый. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>153283</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ЗИЛ-131 бортовой, Автоэкспорт</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-9.jpg</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>10002044</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3050</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>655982</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>КАМАЗ-6520 серый</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-8.jpg</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>10002518</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>557768</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Троллейбус ЗИУ-5 белый</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112604_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112614_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112611_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112608.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112630.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1-(2).jpg</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1062271</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ЗиУ</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>342834</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Автобус ЛиАЗ-677М бело-желтый СОВА</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-6-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1149836</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>483603</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>KAMAZ-65801-T5 самосвал</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-6-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-7-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-8-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1159045</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>7100</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SSM1547</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>694057</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ПУ-20 (51А)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-6.jpg</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1314693</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>221707</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ГЗСА-3711 (53) Почтовый фургон</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/gtk-32-51-657585-5.jpg</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1343751</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SSM1341</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>414794</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Контейнерный мусоровоз M-30 (53)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-11.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-12.jpg</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1388338</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>6100</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>501164</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Автобус Икарус 255.70 антик</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/1-50.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/2-39.jpg</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1440090</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>7100</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>207965</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>БЕЛАЗ-7522 (ранний) карьерный самосвал песочный</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-653275-8.jpg</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2066781</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>БелАЗ</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>SSM1313</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>630928</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>KAMAZ-65225 жёлтый</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-8.jpg</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2075191</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>5300</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>636031</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>СБ-92 (5511) серый бетоносмеситель</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-6.jpg</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2362962</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>214442</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>КРАЗ-214 Мосгортранс</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/241-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/242-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/243-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/244-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/248.jpg</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2428141</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2750</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>КрАЗ</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>472680</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Автобус Икарус 55.14 Ставрополь</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135027_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135038.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135049_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135057_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135107_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135117_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135129.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135143_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135202.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135309_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135323_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135345_1.jpg</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2532465</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>6300</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>655467</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Трамвай Tatra-T3SU синий</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-5.jpg</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2582990</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>7300</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>557767</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Троллейбус ЗИУ-5 красный</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112433.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112444_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112437_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112441_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112455_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2624588</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ЗиУ</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>488956</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Троллейбус ТГ-3</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-6-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-2.jpg</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2771714</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ТГ</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>6463</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Тигр 233001 пикап песочный</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/233001-pikap-11486-1-1.jpg</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3163203</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>189569</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>КАвЗ-3976 (бело-голубой)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240.jpg</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>321488</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>КАвЗ</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>SSM4017</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>621961</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>АКПМ-3 (130)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-6.jpg</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3229352</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>483604</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Автобус Икарус-280 красный</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-6.jpg</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3342857</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>5300</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>280346</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ЗИЛ-ММЗ-585Л самосвал</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-13.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-14.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-9.jpg</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3430175</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ММЗ</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>457283</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>КАМАЗ-65951 самосвал</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-7.jpg</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3466651</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>SSM1533</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>518058</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>БЕЦЕМА АЦ/АТЗ (KAMAZ-65207-87)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-9.jpg</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3563754</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>4250</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>186706</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>КИМ-10-50 Серый (DiP Models)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kim-10-50-seryy-dip-models-ogranichennaya-seriya-5840.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kim-10-50-seryy-dip-models-ogranichennaya-seriya-5840-2.jpg</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3587112</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>КИМ</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>DiP Models</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Смола</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>190502</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Модель новая в боксе.Сертификат идет в комплекте.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>460540</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Автобус Икарус-260.06</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-6.jpg</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>4069148</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>3100</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>441302</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Автобус Икарус 256.54 скарлат</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122158.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122209.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122223_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122220_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122213_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122217_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122229.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122237.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122401.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122422_1.jpg</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>4097841</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>15300</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>291330</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Skoda 706 MTTN с полуприцепом Alka N12CH Schlossberg Sekt</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-9.jpg</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4178680</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>7800</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Škoda</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>507463</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Автобус Икарус-250.58 белый</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055133.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055138.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055143.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055146_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055151.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055156_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055204_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055312_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055329_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351.jpg</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>419962</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>10300</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>199553</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>КАЗ-ММЗ-4502 самосвал</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-15.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-16.jpg</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4250260</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ММЗ</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>SSM1293</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>584696</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>КАМАЗ-6520 рестайлинг самосвал</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-7-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-8-1-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4256288</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>8300</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>326092</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>КАМАЗ-54901 с п/п НЕФАЗ-93341 белый</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/902-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/901-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/904.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/903-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/905.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/907.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/906.jpg</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4381093</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>326092</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>КАМАЗ-54901 с полуприцепом НЕФАЗ-93341</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-11.jpg</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4386018</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>5900</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>696912</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Икарус 222 светло зеленый</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-5.jpg</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>4775954</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>10250</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ModelPro</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Смола</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>559032</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>КО-415А (53213)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-8.jpg</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4840187</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>4150</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>654956</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>KAMAZ-65225 (рестайлинг)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294.jpg</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4849168</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>198946</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>КРАЗ-257Б1 контейнер</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-10.jpg</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>4910920</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>КрАЗ</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>SSM4017</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>633016</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>КАМАЗ-5511 самосвал темно-зеленый</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-6.jpg</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>4912801</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>486148</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>АК-75В (130)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-2-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-7-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-8-3.jpg</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>4986574</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>6250</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>SSM1549</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>472677</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>КАвЗ-651 рапсодия</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/5-18.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/2-23.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/4-19.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/3-20.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/1-30.jpg</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>5014580</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>КАвЗ</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>707012</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>КММ-2 (51)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-9.jpg</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>5048762</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Бачки</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="n">
+        <v>477641</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ikarus-280.64 оранжевый</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-6.jpg</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>5054284</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="n">
+        <v>588726</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>КАМАЗ-6522 рестайлинг желтый</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-7.jpg</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>5085617</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="n">
+        <v>459312</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ЗИЛ-4333 KО-829А поливалка</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-10.jpg</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>5294623</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>342833</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Автобус ЛиАЗ-677М красный СОВА</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-5-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>5698674</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="n">
+        <v>470904</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tatra-815S3 самосвал оранжевый/синий</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-8.jpg</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>5711242</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>6250</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>SSM1538</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="n">
+        <v>488484</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Бокс 32 см (32х9х9) DEMPRICE с винтами</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101849.jpg</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>6122001</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Пластмасса</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Бокс новый.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="n">
+        <v>487535</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>KAMAЗ-43253 Рестайлинг</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-8.jpg</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>6249403</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>5650</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>640208</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>КАМАЗ-43118 рестайлинг</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-8.jpg</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>639065</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="n">
+        <v>473852</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Икарус 250.70 Чили ИНТУРИСТ DEMPRICE</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184241_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184254_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184312_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184333_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184354_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184415.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184450_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184950_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184840_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_185157_1.jpg</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>6455073</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>15300</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="n">
+        <v>342832</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Автобус ЛиАЗ-677М бело-синий СОВА</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-6-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>6498567</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>334587</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Прицеп МАЗ-8926</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-7.jpg</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>6762234</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>МАЗ</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>474035</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Икарус 250.70 клубничный ИНТУРИСТ</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173347.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173351_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173403.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173413.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173417_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173528.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173603_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173612.jpg</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>6773621</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>15300</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>519214</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>KAMAZ-6520-21010-53 самосвал</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-9.jpg</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>7206133</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>4250</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>205299</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>КрАЗ-6322 БРО-200</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-11.jpg</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>7250974</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>2050</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>КрАЗ</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Наш Автопром</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Н947</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="n">
+        <v>507465</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Автобус Икарус-250.58 Совтрансавто</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060555.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060600_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060606_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060611.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060615.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060619_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060627_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060740_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060800.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351-(2).jpg</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>7322725</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>15300</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="n">
+        <v>564883</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>KAMAZ-65952 самосвал</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-7.jpg</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>7408909</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="n">
+        <v>499198</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Икарус-280 белый с красной полосой</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-6.jpg</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>7438713</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>6250</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="n">
+        <v>519215</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>KAMAZ-65207-87 (S5) бортовой</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-8.jpg</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>7494811</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="n">
+        <v>177912</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Полуприцеп МАЗ-5215 зелёный</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-4-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>7640294</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>МАЗ</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>SSM7011</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>474047</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Автобус Икарус 280.33 г. Орёл</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141310.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141318_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141322.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141330_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141335_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141340.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141352_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141456.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141651.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141816.jpg</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>7680062</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>15300</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="n">
+        <v>477068</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>КамАЗ-65802-87 (S5)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-9-1.jpg</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>7722142</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>7150</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>SSM1546</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
+        <v>180403</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>АК-75 (на шасси ЗИЛ-164), голубой/жёлтый</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-14.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-1.jpg</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>7814270</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>5700</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>SSM1129</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>657404</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>КамАЗ-6522 оранжевый</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-8.jpg</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>785738</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>4250</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>441961</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Мусоровоз КО-413 (53) SSM</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/d5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d9.jpg</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>7902021</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>4650</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="n">
+        <v>509636</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>МКЗ-10 (4333)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-7.jpg</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>8192241</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>714392</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ДЭ-210 (ЗИЛ-131)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/legendarnye-gruzoviki-sssr-104-zil-mmz-4510-118824-11.jpg</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>8329937</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>5700</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>SSM1633</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Модель новая. Журнал и открытка в комплекте Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>495095</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PETERBILT 350</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250313_142201.jpg</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>8339384</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>4150</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Peterbilt</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>IXO грузовики (серии TRU)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="n">
+        <v>479880</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AVD троллейбус SKODA-9TR</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115268.jpg</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>8743606</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Škoda</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>AVD Models</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>4021AVD</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="n">
+        <v>630206</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Norba KI-12 (5334) мусоровоз</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-8.jpg</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>8843536</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>6250</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>МАЗ</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="n">
+        <v>472681</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Автобус ЛАЗ-695Н бело-красный</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111725.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111705_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111702.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111708_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111711_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111220_1-(1).jpg</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>8879921</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ЛАЗ</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="n">
+        <v>472729</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Tatra 815 V26 бортовая с тентом</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0021.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0023.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0022.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0024.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0025.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0026.jpg</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>8914544</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>5750</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="n">
+        <v>469263</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Tatra-815S1 самосвал красный</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-9.jpg</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>9007302</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>5750</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>SSM1537</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="n">
+        <v>491552</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Троллейбус Skoda-9TR</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-6.jpg</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>9103969</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>3050</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Škoda</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="n">
+        <v>516931</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>КамАЗ-65802-87 (S5) самосвал</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-9-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-10-1.jpg</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>9158455</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="n">
+        <v>695471</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Полуприцеп НАМИ-790</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-2.jpg</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>9199667</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>НАМИ</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="n">
+        <v>473509</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Автобус Икарус 256.54 Киноварь</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191021_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191025_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191029.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191032_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191036.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191048_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191107_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191147_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191207_1.jpg</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>92437</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>9300</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="n">
+        <v>178808</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Бокс SSM (26,3x10,8x10,9 см)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/boks-ssm-263x108x109-sm-22425.jpg</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>9263175</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Пластмасса</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Бокс новый!Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="n">
+        <v>675784</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ТВГ-15М (51А)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-4.jpg</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>9268253</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="n">
+        <v>557769</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Троллейбус ЗИУ-5 синий, маршрут №41 Москва</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112326_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112331.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112334_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112337_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112350.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1.jpg</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>9523751</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>ЗиУ</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>156421</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Автобус ЗиЛ-158А экскурсионный</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-5.jpg</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>9533455</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="n">
+        <v>666531</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>КАМАЗ-43118 бортовой</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-7.jpg</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>9578983</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="n">
+        <v>221706</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ГЗСА-3723 (53А) Автолавка</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/gorkiy-3307-dvigatel-zmz-513-derev-bort-haki-seryy-23504-6.jpg</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>9798081</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>SSM1340</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="n">
+        <v>473810</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Икарус-250.70 Интурист земляничный</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162825_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162830_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162835_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162845.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163006_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163018_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163042.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163057_1.jpg</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>9840829</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>12300</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3163,34 +3163,34 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>696912</v>
+        <v>717502</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Икарус 222 светло зеленый</t>
+          <t>AVD Автокран КС-3577 (500А)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-5.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/avtokran-ks-3577-500a-666984.jpg</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4775954</t>
+          <t>4636941</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>10250</v>
+        <v>3700</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>МАЗ</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>ModelPro</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3198,12 +3198,12 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Смола</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1707AVD</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Набор новый, запечатанный. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3226,34 +3226,34 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>559032</v>
+        <v>696912</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>КО-415А (53213)</t>
+          <t>Икарус 222 светло зеленый</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-5.jpg</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4840187</t>
+          <t>4775954</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>4150</v>
+        <v>10250</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>ModelPro</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Металл/пластмасса</t>
+          <t>Смола</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3289,25 +3289,25 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>654956</v>
+        <v>559032</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KAMAZ-65225 (рестайлинг)</t>
+          <t>КО-415А (53213)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-8.jpg</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4849168</t>
+          <t>4840187</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3300</v>
+        <v>4150</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3352,34 +3352,34 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>198946</v>
+        <v>654956</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>КРАЗ-257Б1 контейнер</t>
+          <t>KAMAZ-65225 (рестайлинг)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-10.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294.jpg</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4910920</t>
+          <t>4849168</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3800</v>
+        <v>3300</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>КрАЗ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3392,11 +3392,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>SSM4017</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3419,34 +3415,34 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>633016</v>
+        <v>198946</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>КАМАЗ-5511 самосвал темно-зеленый</t>
+          <t>КРАЗ-257Б1 контейнер</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-10.jpg</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4912801</t>
+          <t>4910920</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>6200</v>
+        <v>3800</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>КрАЗ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3454,8 +3450,16 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>SSM4017</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3463,7 +3467,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3478,34 +3482,34 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>486148</v>
+        <v>633016</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>АК-75В (130)</t>
+          <t>КАМАЗ-5511 самосвал темно-зеленый</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-2-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-7-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-8-3.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-6.jpg</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>4986574</t>
+          <t>4912801</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6250</v>
+        <v>6200</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3513,16 +3517,8 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>SSM1549</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3545,34 +3541,34 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>472677</v>
+        <v>486148</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>КАвЗ-651 рапсодия</t>
+          <t>АК-75В (130)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/5-18.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/2-23.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/4-19.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/3-20.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/1-30.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-2-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-7-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-8-3.jpg</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>5014580</t>
+          <t>4986574</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>3250</v>
+        <v>6250</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>КАвЗ</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3585,7 +3581,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>SSM1549</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3608,34 +3608,34 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>707012</v>
+        <v>472677</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>КММ-2 (51)</t>
+          <t>КАвЗ-651 рапсодия</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/5-18.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/2-23.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/4-19.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/3-20.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/1-30.jpg</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5048762</t>
+          <t>5014580</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>6200</v>
+        <v>3250</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>КАвЗ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3648,11 +3648,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Бачки</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3660,7 +3656,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3675,34 +3671,34 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>477641</v>
+        <v>707012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ikarus-280.64 оранжевый</t>
+          <t>КММ-2 (51)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-9.jpg</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>5054284</t>
+          <t>5048762</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>6800</v>
+        <v>6200</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3715,7 +3711,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Бачки</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3738,21 +3738,21 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>588726</v>
+        <v>477641</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>КАМАЗ-6522 рестайлинг желтый</t>
+          <t>Ikarus-280.64 оранжевый</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-6.jpg</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5085617</t>
+          <t>5054284</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3801,29 +3801,29 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>459312</v>
+        <v>588726</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ЗИЛ-4333 KО-829А поливалка</t>
+          <t>КАМАЗ-6522 рестайлинг желтый</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-10.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-7.jpg</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>5294623</t>
+          <t>5085617</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>5250</v>
+        <v>6800</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3864,34 +3864,34 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>342833</v>
+        <v>459312</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Автобус ЛиАЗ-677М красный СОВА</t>
+          <t>ЗИЛ-4333 KО-829А поливалка</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-5-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-10.jpg</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>5698674</t>
+          <t>5294623</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3300</v>
+        <v>5250</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3927,34 +3927,34 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>470904</v>
+        <v>342833</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tatra-815S3 самосвал оранжевый/синий</t>
+          <t>Автобус ЛиАЗ-677М красный СОВА</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-5-(1).jpg</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5711242</t>
+          <t>5698674</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>6250</v>
+        <v>3300</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>ЛиАЗ</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3967,11 +3967,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>SSM1538</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3994,34 +3990,34 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>488484</v>
+        <v>470904</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Бокс 32 см (32х9х9) DEMPRICE с винтами</t>
+          <t>Tatra-815S3 самосвал оранжевый/синий</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101849.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-8.jpg</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6122001</t>
+          <t>5711242</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1250</v>
+        <v>6250</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4031,10 +4027,14 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Пластмасса</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>SSM1538</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Бокс новый.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4057,34 +4057,34 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>487535</v>
+        <v>488484</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KAMAЗ-43253 Рестайлинг</t>
+          <t>Бокс 32 см (32х9х9) DEMPRICE с винтами</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101849.jpg</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6249403</t>
+          <t>6122001</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>5650</v>
+        <v>1250</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Металл/пластмасса</t>
+          <t>Пластмасса</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Бокс новый.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4120,25 +4120,25 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>640208</v>
+        <v>487535</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>КАМАЗ-43118 рестайлинг</t>
+          <t>KAMAЗ-43253 Рестайлинг</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-8.jpg</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>639065</t>
+          <t>6249403</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>4900</v>
+        <v>5650</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4183,34 +4183,34 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>473852</v>
+        <v>640208</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Икарус 250.70 Чили ИНТУРИСТ DEMPRICE</t>
+          <t>КАМАЗ-43118 рестайлинг</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184241_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184254_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184312_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184333_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184354_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184415.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184450_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184950_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184840_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_185157_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-8.jpg</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>6455073</t>
+          <t>639065</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>15300</v>
+        <v>4900</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4246,34 +4246,34 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>342832</v>
+        <v>473852</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Автобус ЛиАЗ-677М бело-синий СОВА</t>
+          <t>Икарус 250.70 Чили ИНТУРИСТ DEMPRICE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-6-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184241_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184254_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184312_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184333_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184354_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184415.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184450_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184950_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184840_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_185157_1.jpg</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>6498567</t>
+          <t>6455073</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3250</v>
+        <v>15300</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4309,34 +4309,34 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>334587</v>
+        <v>342832</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Прицеп МАЗ-8926</t>
+          <t>Автобус ЛиАЗ-677М бело-синий СОВА</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-6-(1).jpg</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>6762234</t>
+          <t>6498567</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2250</v>
+        <v>3250</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>МАЗ</t>
+          <t>ЛиАЗ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4372,34 +4372,34 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>474035</v>
+        <v>334587</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Икарус 250.70 клубничный ИНТУРИСТ</t>
+          <t>Прицеп МАЗ-8926</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173347.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173351_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173403.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173413.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173417_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173528.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173603_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173612.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-7.jpg</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>6773621</t>
+          <t>6762234</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>15300</v>
+        <v>2250</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>МАЗ</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4435,34 +4435,34 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>519214</v>
+        <v>474035</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>KAMAZ-6520-21010-53 самосвал</t>
+          <t>Икарус 250.70 клубничный ИНТУРИСТ</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173347.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173351_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173403.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173413.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173417_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173528.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173603_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173612.jpg</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>7206133</t>
+          <t>6773621</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>4250</v>
+        <v>15300</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4498,34 +4498,34 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>205299</v>
+        <v>519214</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>КрАЗ-6322 БРО-200</t>
+          <t>KAMAZ-6520-21010-53 самосвал</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-11.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-9.jpg</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>7250974</t>
+          <t>7206133</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2050</v>
+        <v>4250</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>КрАЗ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Наш Автопром</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4538,11 +4538,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Н947</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4565,34 +4561,34 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>507465</v>
+        <v>205299</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Автобус Икарус-250.58 Совтрансавто</t>
+          <t>КрАЗ-6322 БРО-200</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060555.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060600_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060606_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060611.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060615.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060619_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060627_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060740_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060800.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351-(2).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-11.jpg</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>7322725</t>
+          <t>7250974</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>15300</v>
+        <v>2050</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>КрАЗ</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Наш Автопром</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4605,7 +4601,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Н947</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4628,34 +4628,34 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>564883</v>
+        <v>507465</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KAMAZ-65952 самосвал</t>
+          <t>Автобус Икарус-250.58 Совтрансавто</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060555.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060600_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060606_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060611.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060615.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060619_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060627_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060740_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060800.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351-(2).jpg</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>7408909</t>
+          <t>7322725</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>4200</v>
+        <v>15300</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -4691,34 +4691,34 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>499198</v>
+        <v>564883</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Икарус-280 белый с красной полосой</t>
+          <t>KAMAZ-65952 самосвал</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-7.jpg</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>7438713</t>
+          <t>7408909</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>6250</v>
+        <v>4200</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -4754,34 +4754,34 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>519215</v>
+        <v>499198</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KAMAZ-65207-87 (S5) бортовой</t>
+          <t>Икарус-280 белый с красной полосой</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-6.jpg</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>7494811</t>
+          <t>7438713</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>4900</v>
+        <v>6250</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -4817,34 +4817,34 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>177912</v>
+        <v>519215</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Полуприцеп МАЗ-5215 зелёный</t>
+          <t>KAMAZ-65207-87 (S5) бортовой</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-4-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-8.jpg</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>7640294</t>
+          <t>7494811</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1750</v>
+        <v>4900</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>МАЗ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4857,11 +4857,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>SSM7011</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4884,34 +4880,34 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>474047</v>
+        <v>177912</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Автобус Икарус 280.33 г. Орёл</t>
+          <t>Полуприцеп МАЗ-5215 зелёный</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141310.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141318_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141322.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141330_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141335_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141340.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141352_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141456.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141651.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141816.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-4-(1).jpg</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>7680062</t>
+          <t>7640294</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>15300</v>
+        <v>1750</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>МАЗ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4919,8 +4915,16 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>SSM7011</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4928,7 +4932,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -4943,34 +4947,34 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>477068</v>
+        <v>474047</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>КамАЗ-65802-87 (S5)</t>
+          <t>Автобус Икарус 280.33 г. Орёл</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-9-1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141310.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141318_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141322.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141330_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141335_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141340.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141352_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141456.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141651.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141816.jpg</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>7722142</t>
+          <t>7680062</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>7150</v>
+        <v>15300</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4978,16 +4982,8 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>SSM1546</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4995,7 +4991,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5010,29 +5006,29 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>180403</v>
+        <v>477068</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>АК-75 (на шасси ЗИЛ-164), голубой/жёлтый</t>
+          <t>КамАЗ-65802-87 (S5)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-14.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-9-1.jpg</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>7814270</t>
+          <t>7722142</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>5700</v>
+        <v>7150</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5052,7 +5048,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>SSM1129</t>
+          <t>SSM1546</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5062,7 +5058,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5077,34 +5073,34 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>657404</v>
+        <v>180403</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>КамАЗ-6522 оранжевый</t>
+          <t>АК-75 (на шасси ЗИЛ-164), голубой/жёлтый</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-14.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-1.jpg</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>785738</t>
+          <t>7814270</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>4250</v>
+        <v>5700</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5117,7 +5113,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>SSM1129</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5140,34 +5140,34 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>441961</v>
+        <v>657404</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Мусоровоз КО-413 (53) SSM</t>
+          <t>КамАЗ-6522 оранжевый</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/d5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-8.jpg</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>7902021</t>
+          <t>785738</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>4650</v>
+        <v>4250</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5203,34 +5203,34 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>509636</v>
+        <v>441961</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>МКЗ-10 (4333)</t>
+          <t>Мусоровоз КО-413 (53) SSM</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/d5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d9.jpg</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>8192241</t>
+          <t>7902021</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2250</v>
+        <v>4650</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5266,25 +5266,25 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>714392</v>
+        <v>509636</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ДЭ-210 (ЗИЛ-131)</t>
+          <t>МКЗ-10 (4333)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/legendarnye-gruzoviki-sssr-104-zil-mmz-4510-118824-11.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-7.jpg</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>8329937</t>
+          <t>8192241</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>5700</v>
+        <v>2250</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5306,11 +5306,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>SSM1633</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5318,7 +5314,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Модель новая. Журнал и открытка в комплекте Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5333,34 +5329,34 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>495095</v>
+        <v>714392</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PETERBILT 350</t>
+          <t>ДЭ-210 (ЗИЛ-131)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250313_142201.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/legendarnye-gruzoviki-sssr-104-zil-mmz-4510-118824-11.jpg</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>8339384</t>
+          <t>8329937</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>4150</v>
+        <v>5700</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Peterbilt</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>IXO грузовики (серии TRU)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5368,8 +5364,16 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>SSM1633</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5377,7 +5381,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Журнал и открытка в комплекте Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5392,34 +5396,34 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>479880</v>
+        <v>495095</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AVD троллейбус SKODA-9TR</t>
+          <t>PETERBILT 350</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115268.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250313_142201.jpg</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>8743606</t>
+          <t>8339384</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2500</v>
+        <v>4150</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Škoda</t>
+          <t>Peterbilt</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>AVD Models</t>
+          <t>IXO грузовики (серии TRU)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5427,16 +5431,8 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>4021AVD</t>
-        </is>
-      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5459,34 +5455,34 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>630206</v>
+        <v>479880</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Norba KI-12 (5334) мусоровоз</t>
+          <t>AVD троллейбус SKODA-9TR</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115268.jpg</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>8843536</t>
+          <t>8743606</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>6250</v>
+        <v>2500</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>МАЗ</t>
+          <t>Škoda</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5499,7 +5495,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>4021AVD</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5522,34 +5522,34 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>472681</v>
+        <v>630206</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Автобус ЛАЗ-695Н бело-красный</t>
+          <t>Norba KI-12 (5334) мусоровоз</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111725.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111705_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111702.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111708_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111711_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111220_1-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-8.jpg</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>8879921</t>
+          <t>8843536</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>5800</v>
+        <v>6250</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>ЛАЗ</t>
+          <t>МАЗ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5585,34 +5585,34 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>472729</v>
+        <v>472681</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tatra 815 V26 бортовая с тентом</t>
+          <t>Автобус ЛАЗ-695Н бело-красный</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0021.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0023.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0022.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0024.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0025.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0026.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111725.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111705_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111702.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111708_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111711_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111220_1-(1).jpg</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>8914544</t>
+          <t>8879921</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>5750</v>
+        <v>5800</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>ЛАЗ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -5648,21 +5648,21 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>469263</v>
+        <v>472729</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tatra-815S1 самосвал красный</t>
+          <t>Tatra 815 V26 бортовая с тентом</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0021.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0023.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0022.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0024.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0025.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0026.jpg</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>9007302</t>
+          <t>8914544</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5688,11 +5688,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>SSM1537</t>
-        </is>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5715,34 +5711,34 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>491552</v>
+        <v>469263</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Троллейбус Skoda-9TR</t>
+          <t>Tatra-815S1 самосвал красный</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-9.jpg</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>9103969</t>
+          <t>9007302</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3050</v>
+        <v>5750</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Škoda</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5755,7 +5751,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>SSM1537</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -5778,29 +5778,29 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>516931</v>
+        <v>491552</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>КамАЗ-65802-87 (S5) самосвал</t>
+          <t>Троллейбус Skoda-9TR</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-9-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-10-1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-6.jpg</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>9158455</t>
+          <t>9103969</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>5250</v>
+        <v>3050</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Škoda</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5841,29 +5841,29 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>695471</v>
+        <v>516931</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Полуприцеп НАМИ-790</t>
+          <t>КамАЗ-65802-87 (S5) самосвал</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-2.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-9-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-10-1.jpg</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>9199667</t>
+          <t>9158455</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3750</v>
+        <v>5250</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>НАМИ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5904,34 +5904,34 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>473509</v>
+        <v>695471</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Автобус Икарус 256.54 Киноварь</t>
+          <t>Полуприцеп НАМИ-790</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191021_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191025_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191029.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191032_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191036.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191048_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191107_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191147_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191207_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-2.jpg</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>92437</t>
+          <t>9199667</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>9300</v>
+        <v>3750</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>НАМИ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -5967,36 +5967,44 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>178808</v>
+        <v>473509</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Бокс SSM (26,3x10,8x10,9 см)</t>
+          <t>Автобус Икарус 256.54 Киноварь</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/boks-ssm-263x108x109-sm-22425.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191021_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191025_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191029.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191032_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191036.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191048_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191107_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191147_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191207_1.jpg</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>9263175</t>
+          <t>92437</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1050</v>
-      </c>
-      <c r="G88" t="inlineStr"/>
+        <v>9300</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Пластмасса</t>
+          <t>Металл/пластмасса</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -6007,7 +6015,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Бокс новый!Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6022,44 +6030,36 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>675784</v>
+        <v>178808</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ТВГ-15М (51А)</t>
+          <t>Бокс SSM (26,3x10,8x10,9 см)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-4.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/boks-ssm-263x108x109-sm-22425.jpg</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>9268253</t>
+          <t>9263175</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Горький</t>
-        </is>
-      </c>
+        <v>1050</v>
+      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>Start Scale Models (SSM)</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Металл/пластмасса</t>
+          <t>Пластмасса</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Бокс новый!Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6085,34 +6085,34 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>557769</v>
+        <v>675784</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Троллейбус ЗИУ-5 синий, маршрут №41 Москва</t>
+          <t>ТВГ-15М (51А)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112326_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112331.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112334_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112337_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112350.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-4.jpg</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>9523751</t>
+          <t>9268253</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>7200</v>
+        <v>5800</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>ЗиУ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6148,34 +6148,34 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>156421</v>
+        <v>557769</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Автобус ЗиЛ-158А экскурсионный</t>
+          <t>Троллейбус ЗИУ-5 синий, маршрут №41 Москва</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-5.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112326_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112331.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112334_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112337_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112350.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1.jpg</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>9533455</t>
+          <t>9523751</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1850</v>
+        <v>7200</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>ЗиУ</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6211,34 +6211,34 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>666531</v>
+        <v>156421</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>КАМАЗ-43118 бортовой</t>
+          <t>Автобус ЗиЛ-158А экскурсионный</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-5.jpg</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>9578983</t>
+          <t>9533455</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3800</v>
+        <v>1850</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6274,34 +6274,34 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>221706</v>
+        <v>666531</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ГЗСА-3723 (53А) Автолавка</t>
+          <t>КАМАЗ-43118 бортовой</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/gorkiy-3307-dvigatel-zmz-513-derev-bort-haki-seryy-23504-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-7.jpg</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>9798081</t>
+          <t>9578983</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2800</v>
+        <v>3800</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6314,11 +6314,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>SSM1340</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -6341,34 +6337,34 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>473810</v>
+        <v>637799</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Икарус-250.70 Интурист земляничный</t>
+          <t>AVD Пожарная автолестница АЛМ-30 (157)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162825_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162830_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162835_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162845.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163006_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163018_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163042.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163057_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pozharnaya-avtolestnica-alm-30-157-655277.jpg</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>9840829</t>
+          <t>9675080</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>12300</v>
+        <v>3055</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6389,15 +6385,145 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
+          <t>Набор новый, в пленке. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="n">
+        <v>221706</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ГЗСА-3723 (53А) Автолавка</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/gorkiy-3307-dvigatel-zmz-513-derev-bort-haki-seryy-23504-6.jpg</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>9798081</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>SSM1340</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="n">
+        <v>473810</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Икарус-250.70 Интурист земляничный</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162825_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162830_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162835_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162845.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163006_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163018_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163042.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163057_1.jpg</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>9840829</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>12300</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
           <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>г Химки, кв-л Клязьма</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O96"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,34 +686,34 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>725366</v>
+        <v>486775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>КАМАЗ-65115 самосвал желтый</t>
+          <t>Икарус 280.64 бело/красный</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115243-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115243-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115243-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115243.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115243-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115243-6.jpg</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10000940</t>
+          <t>10000938</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6800</v>
+        <v>5250</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -726,11 +726,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>SSM1656</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>новый</t>
@@ -738,7 +734,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;img src="https://ritmonexx.ru/images/cache/additional/800x600/kamaz-65115-666976-5.jpg?54fc43e543c281fc5898076f12b0b2c0" alt="kamaz-65115-666976-5.jpg?54fc43e543c281fc5898076f12b0b2c0" /&gt;&lt;/p&gt;&lt;p&gt;&lt;img src="https://ritmonexx.ru/images/cache/additional/800x600/kamaz-65115-666976-8.jpg?14749c9c96ed9bb6482af2a8e8b5e44b" alt="kamaz-65115-666976-8.jpg?14749c9c96ed9bb6482af2a8e8b5e44b" /&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -753,34 +749,34 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>356447</v>
+        <v>499197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>КАМАЗ-54901 с полуприцепом НЕФАЗ-93341</t>
+          <t>Икарус 280.64 бело/синий</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/932-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/931-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/933-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/935-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/934-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/937.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/936.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/938.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/939.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115244.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115244-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115244-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115244-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115244-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115244-6.jpg</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10001182</t>
+          <t>10000939</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5200</v>
+        <v>6250</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -816,34 +812,34 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>707012</v>
+        <v>725366</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>КММ-2 (51)</t>
+          <t>КАМАЗ-65115 самосвал желтый</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-2.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65115-666976-8.jpg</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10001183</t>
+          <t>10000940</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3250</v>
+        <v>6800</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -856,7 +852,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SSM1656</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>новый</t>
@@ -864,7 +864,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;img src="https://ritmonexx.ru/images/cache/additional/800x600/kamaz-65115-666976-5.jpg?54fc43e543c281fc5898076f12b0b2c0" alt="kamaz-65115-666976-5.jpg?54fc43e543c281fc5898076f12b0b2c0" /&gt;&lt;/p&gt;&lt;p&gt;&lt;img src="https://ritmonexx.ru/images/cache/additional/800x600/kamaz-65115-666976-8.jpg?14749c9c96ed9bb6482af2a8e8b5e44b" alt="kamaz-65115-666976-8.jpg?14749c9c96ed9bb6482af2a8e8b5e44b" /&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -879,34 +879,34 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>509635</v>
+        <v>356447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>КО-829А (4333) поливалка</t>
+          <t>КАМАЗ-54901 с полуприцепом НЕФАЗ-93341</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/932-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/931-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/933-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/935-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/934-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/937.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/936.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/938.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/939.jpg</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10001581</t>
+          <t>10001182</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2250</v>
+        <v>5200</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -942,34 +942,34 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>507464</v>
+        <v>707012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Автобус Икарус-250.58 Интурбюро</t>
+          <t>КММ-2 (51)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055945.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055951.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055955_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055959.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060002_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060008.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060019.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060133_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060150_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-120753-2.jpg</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10001836</t>
+          <t>10001183</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10200</v>
+        <v>3250</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1005,36 +1005,44 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>151979</v>
+        <v>316257</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Бокс SSM (19x8x8 см)</t>
+          <t>Автобус Икарус-260 планетарные двери (жёлтый)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/sredniy-boks-ssm-19x8x8-sm-12270.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/26003zh-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/26003zh-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/26003zh-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/26003zh-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/26003zh-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/26003zh-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/26003zh-7.jpg</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10001886</t>
+          <t>10001271</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>690</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
+        <v>4550</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Пластмасса</t>
+          <t>Металл/пластмасса</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1045,7 +1053,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Бокс новый. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1060,25 +1068,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>153283</v>
+        <v>509635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ЗИЛ-131 бортовой, Автоэкспорт</t>
+          <t>КО-829А (4333) поливалка</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-829a-4333-111676-8.jpg</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10002044</t>
+          <t>10001581</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3050</v>
+        <v>2250</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1087,7 +1095,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1108,7 +1116,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1123,34 +1131,34 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>655982</v>
+        <v>507464</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>КАМАЗ-6520 серый</t>
+          <t>Автобус Икарус-250.58 Интурбюро</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055945.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055951.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055955_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055959.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060002_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060008.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060019.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060133_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060150_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351-(1).jpg</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10002518</t>
+          <t>10001836</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3300</v>
+        <v>10200</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1171,7 +1179,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Модель новая.&lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.&lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1186,55 +1194,47 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>557768</v>
+        <v>151979</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Троллейбус ЗИУ-5 белый</t>
+          <t>Бокс SSM (19x8x8 см)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112604_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112614_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112611_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112608.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112630.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1-(2).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/sredniy-boks-ssm-19x8x8-sm-12270.jpg</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1062271</t>
+          <t>10001886</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7200</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ЗиУ</t>
-        </is>
-      </c>
+        <v>690</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Металл/пластмасса</t>
+          <t>Пластмасса</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Новый</t>
+          <t>новый</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>&lt;p&gt;Бокс новый. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1249,34 +1249,34 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>342834</v>
+        <v>153283</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Автобус ЛиАЗ-677М бело-желтый СОВА</t>
+          <t>ЗИЛ-131 бортовой, Автоэкспорт</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-6-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-131-bortovoy-avtoeksport-12549-9.jpg</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1149836</t>
+          <t>10002044</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3300</v>
+        <v>3050</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1292,12 +1292,12 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Новый</t>
+          <t>новый</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1312,34 +1312,34 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>483603</v>
+        <v>488096</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KAMAZ-65801-T5 самосвал</t>
+          <t>КАвЗ-3270 бело-красный</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-6-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-7-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-8-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/avtobus-3270-113957-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/avtobus-3270-113957-2-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/avtobus-3270-113957-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/avtobus-3270-113957-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/avtobus-3270-113957-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/avtobus-3270-113957-6-1.jpg</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1159045</t>
+          <t>10002293</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7100</v>
+        <v>2700</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>КАвЗ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1352,19 +1352,15 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>SSM1547</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Новый</t>
+          <t>новый</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1379,34 +1375,34 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>694057</v>
+        <v>655982</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ПУ-20 (51А)</t>
+          <t>КАМАЗ-6520 серый</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-655293-8.jpg</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1314693</t>
+          <t>10002518</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2900</v>
+        <v>3300</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1422,12 +1418,12 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Новый</t>
+          <t>новый</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>&lt;p&gt;Модель новая. &lt;/p&gt;&lt;p&gt;Самовывоз возможен только в г. Химки (Набережный проезд 3).&lt;/p&gt;&lt;p&gt;Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. &lt;/p&gt;&lt;p&gt;Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1442,34 +1438,34 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>221707</v>
+        <v>557768</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ГЗСА-3711 (53) Почтовый фургон</t>
+          <t>Троллейбус ЗИУ-5 белый</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/gtk-32-51-657585-5.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112604_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112614_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112611_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112608.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112630.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1-(2).jpg</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1343751</t>
+          <t>1062271</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2800</v>
+        <v>7200</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>ЗиУ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1482,11 +1478,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>SSM1341</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -1494,7 +1486,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1509,34 +1501,34 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>414794</v>
+        <v>342834</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Контейнерный мусоровоз M-30 (53)</t>
+          <t>Автобус ЛиАЗ-677М бело-желтый СОВА</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-11.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-12.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbzh-6-(1).jpg</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1388338</t>
+          <t>1149836</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6100</v>
+        <v>3300</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>ЛиАЗ</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1557,7 +1549,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1572,21 +1564,21 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>501164</v>
+        <v>483603</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Автобус Икарус 255.70 антик</t>
+          <t>KAMAZ-65801-T5 самосвал</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/1-50.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/2-39.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-6-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-7-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65801-t5-115149-8-(1).jpg</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1440090</t>
+          <t>1159045</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1594,12 +1586,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1612,7 +1604,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SSM1547</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -1620,7 +1616,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1635,34 +1631,34 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>207965</v>
+        <v>694057</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>БЕЛАЗ-7522 (ранний) карьерный самосвал песочный</t>
+          <t>ПУ-20 (51А)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-653275-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pu-20-51a-650582-6.jpg</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2066781</t>
+          <t>1314693</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5800</v>
+        <v>2900</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>БелАЗ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1675,11 +1671,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>SSM1313</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -1702,29 +1694,29 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>630928</v>
+        <v>221707</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KAMAZ-65225 жёлтый</t>
+          <t>ГЗСА-3711 (53) Почтовый фургон</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/gtk-32-51-657585-5.jpg</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2075191</t>
+          <t>1343751</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5300</v>
+        <v>2800</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1742,7 +1734,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>SSM1341</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -1765,34 +1761,34 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>636031</v>
+        <v>414794</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>СБ-92 (5511) серый бетоносмеситель</t>
+          <t>Контейнерный мусоровоз M-30 (53)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-11.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/m-30-53-110639-12.jpg</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2362962</t>
+          <t>1388338</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4800</v>
+        <v>6100</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1813,7 +1809,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1828,34 +1824,34 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>214442</v>
+        <v>501164</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>КРАЗ-214 Мосгортранс</t>
+          <t>Автобус Икарус 255.70 антик</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/241-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/242-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/243-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/244-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/248.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/1-50.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/2-39.jpg</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2428141</t>
+          <t>1440090</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2750</v>
+        <v>7100</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>КрАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,34 +1887,34 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>472680</v>
+        <v>207965</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Автобус Икарус 55.14 Ставрополь</t>
+          <t>БЕЛАЗ-7522 (ранний) карьерный самосвал песочный</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135027_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135038.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135049_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135057_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135107_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135117_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135129.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135143_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135202.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135309_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135323_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135345_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-653275-8.jpg</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2532465</t>
+          <t>2066781</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6300</v>
+        <v>5800</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>БелАЗ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1931,7 +1927,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>SSM1313</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1954,29 +1954,29 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>655467</v>
+        <v>630928</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Трамвай Tatra-T3SU синий</t>
+          <t>KAMAZ-65225 жёлтый</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-5.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-653271-8.jpg</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2582990</t>
+          <t>2075191</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7300</v>
+        <v>5300</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2017,34 +2017,34 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>557767</v>
+        <v>636031</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Троллейбус ЗИУ-5 красный</t>
+          <t>СБ-92 (5511) серый бетоносмеситель</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112433.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112444_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112437_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112441_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112455_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/sb-92-5511-114065-6.jpg</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2624588</t>
+          <t>2362962</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>7200</v>
+        <v>4800</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ЗиУ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2080,34 +2080,34 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>488956</v>
+        <v>214442</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Троллейбус ТГ-3</t>
+          <t>КРАЗ-214 Мосгортранс</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-6-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-2.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/241-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/242-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/243-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/244-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/248.jpg</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2771714</t>
+          <t>2428141</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2850</v>
+        <v>2750</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ТГ</t>
+          <t>КрАЗ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2143,34 +2143,34 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>6463</v>
+        <v>472680</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Тигр 233001 пикап песочный</t>
+          <t>Автобус Икарус 55.14 Ставрополь</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/233001-pikap-11486-1-1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135027_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135038.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135049_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135057_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135107_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135117_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135129.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135143_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135202.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135309_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135323_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230707_135345_1.jpg</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3163203</t>
+          <t>2532465</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1650</v>
+        <v>6300</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2206,29 +2206,29 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>189569</v>
+        <v>655467</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>КАвЗ-3976 (бело-голубой)</t>
+          <t>Трамвай Tatra-T3SU синий</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-t3su-106304-5.jpg</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>321488</t>
+          <t>2582990</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4800</v>
+        <v>7300</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>КАвЗ</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2246,11 +2246,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>SSM4017</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -2273,34 +2269,34 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>621961</v>
+        <v>557767</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>АКПМ-3 (130)</t>
+          <t>Троллейбус ЗИУ-5 красный</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112433.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112444_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112437_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112441_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112455_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1-(1).jpg</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3229352</t>
+          <t>2624588</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2800</v>
+        <v>7200</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>ЗиУ</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2321,7 +2317,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2336,29 +2332,29 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>483604</v>
+        <v>338229</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Автобус Икарус-280 красный</t>
+          <t>ПАЗ-3205 бело-зеленый</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/paz-3205-91120.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/paz-3205-91120-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/paz-3205-91120-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/paz-3205-91120-3.jpg</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3342857</t>
+          <t>2708367</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5300</v>
+        <v>3500</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>ПАЗ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2384,7 +2380,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2399,34 +2395,34 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>280346</v>
+        <v>488956</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ЗИЛ-ММЗ-585Л самосвал</t>
+          <t>Троллейбус ТГ-3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-13.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-14.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-6-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tg-3-117331-2.jpg</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3430175</t>
+          <t>2771714</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6800</v>
+        <v>2850</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ММЗ</t>
+          <t>ТГ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2434,7 +2430,11 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
@@ -2458,29 +2458,29 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>457283</v>
+        <v>6463</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>КАМАЗ-65951 самосвал</t>
+          <t>Тигр 233001 пикап песочный</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/233001-pikap-11486-1-1.jpg</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3466651</t>
+          <t>3163203</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6800</v>
+        <v>1650</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2498,11 +2498,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>SSM1533</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -2525,34 +2521,34 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>518058</v>
+        <v>189569</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>БЕЦЕМА АЦ/АТЗ (KAMAZ-65207-87)</t>
+          <t>КАвЗ-3976 (бело-голубой)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/prigorodnyy-kurganskiy-avtobus-3976-belo-goluboy-31240.jpg</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3563754</t>
+          <t>321488</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4250</v>
+        <v>4800</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>КАвЗ</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2565,7 +2561,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>SSM4017</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -2588,34 +2588,34 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>186706</v>
+        <v>621961</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>КИМ-10-50 Серый (DiP Models)</t>
+          <t>АКПМ-3 (130)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kim-10-50-seryy-dip-models-ogranichennaya-seriya-5840.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kim-10-50-seryy-dip-models-ogranichennaya-seriya-5840-2.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/akpm-3-130-zelenyy-oranzhevyy-651433-6.jpg</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3587112</t>
+          <t>3229352</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1600</v>
+        <v>2800</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>КИМ</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>DiP Models</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2625,14 +2625,10 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Смола</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>190502</t>
-        </is>
-      </c>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -2640,7 +2636,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Модель новая в боксе.Сертификат идет в комплекте.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2655,25 +2651,25 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>460540</v>
+        <v>483604</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Автобус Икарус-260.06</t>
+          <t>Автобус Икарус-280 красный</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115246-6.jpg</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4069148</t>
+          <t>3342857</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3100</v>
+        <v>5300</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2718,34 +2714,34 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>441302</v>
+        <v>280346</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Автобус Икарус 256.54 скарлат</t>
+          <t>ЗИЛ-ММЗ-585Л самосвал</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122158.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122209.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122223_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122220_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122213_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122217_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122229.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122237.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122401.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122422_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-13.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-14.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-mmz-585l-samosval-77361-9.jpg</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4097841</t>
+          <t>3430175</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>15300</v>
+        <v>6800</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>ММЗ</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2753,11 +2749,7 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
@@ -2766,7 +2758,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2781,29 +2773,29 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>291330</v>
+        <v>457283</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Skoda 706 MTTN с полуприцепом Alka N12CH Schlossberg Sekt</t>
+          <t>КАМАЗ-65951 самосвал</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65951-samosval-112925-7.jpg</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4178680</t>
+          <t>3466651</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>7800</v>
+        <v>6800</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Škoda</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2821,7 +2813,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>SSM1533</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -2844,34 +2840,34 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>507463</v>
+        <v>518058</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Автобус Икарус-250.58 белый</t>
+          <t>БЕЦЕМА АЦ/АТЗ (KAMAZ-65207-87)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055133.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055138.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055143.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055146_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055151.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055156_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055204_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055312_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055329_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/becema-ac-atz-kamaz-65207-87-116156-9.jpg</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>419962</t>
+          <t>3563754</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>10300</v>
+        <v>4250</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2892,7 +2888,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2907,34 +2903,34 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>199553</v>
+        <v>186706</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>КАЗ-ММЗ-4502 самосвал</t>
+          <t>КИМ-10-50 Серый (DiP Models)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-15.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-16.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kim-10-50-seryy-dip-models-ogranichennaya-seriya-5840.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kim-10-50-seryy-dip-models-ogranichennaya-seriya-5840-2.jpg</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4250260</t>
+          <t>3587112</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2600</v>
+        <v>1600</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ММЗ</t>
+          <t>КИМ</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DiP Models</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2944,12 +2940,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Металл/пластмасса</t>
+          <t>Смола</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SSM1293</t>
+          <t>190502</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2959,7 +2955,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая в боксе.Сертификат идет в комплекте.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2974,34 +2970,34 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>584696</v>
+        <v>460540</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>КАМАЗ-6520 рестайлинг самосвал</t>
+          <t>Автобус Икарус-260.06</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-7-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-8-1-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-06-113836-6.jpg</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4256288</t>
+          <t>4069148</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>8300</v>
+        <v>3100</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3022,7 +3018,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3037,34 +3033,34 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>326092</v>
+        <v>441302</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>КАМАЗ-54901 с п/п НЕФАЗ-93341 белый</t>
+          <t>Автобус Икарус 256.54 скарлат</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/902-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/901-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/904.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/903-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/905.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/907.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/906.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122158.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122209.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122223_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122220_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122213_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122217_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122229.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122237.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122401.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230821_122422_1.jpg</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4381093</t>
+          <t>4097841</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>6800</v>
+        <v>15300</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3100,34 +3096,34 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>326092</v>
+        <v>291330</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>КАМАЗ-54901 с полуприцепом НЕФАЗ-93341</t>
+          <t>Skoda 706 MTTN с полуприцепом Alka N12CH Schlossberg Sekt</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-11.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-706-mttn-s-polupricepom-alka-n12ch-schlossberg-sekt-77939-9.jpg</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4386018</t>
+          <t>4178680</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>5900</v>
+        <v>7800</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Škoda</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3148,7 +3144,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3163,34 +3159,34 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>717502</v>
+        <v>507463</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AVD Автокран КС-3577 (500А)</t>
+          <t>Автобус Икарус-250.58 белый</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/avtokran-ks-3577-500a-666984.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055133.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055138.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055143.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055146_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055151.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055156_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055204_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055312_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055329_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351.jpg</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4636941</t>
+          <t>419962</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3700</v>
+        <v>10300</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>МАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>AVD Models</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3198,12 +3194,12 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>1707AVD</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3211,7 +3207,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Набор новый, запечатанный. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3226,34 +3222,34 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>696912</v>
+        <v>199553</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Икарус 222 светло зеленый</t>
+          <t>КАЗ-ММЗ-4502 самосвал</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-5.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-15.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kaz-mmz-4502-samosval-38727-16.jpg</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4775954</t>
+          <t>4250260</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>10250</v>
+        <v>2600</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>ММЗ</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>ModelPro</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3263,10 +3259,14 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Смола</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>SSM1293</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3289,25 +3289,25 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>559032</v>
+        <v>584696</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>КО-415А (53213)</t>
+          <t>КАМАЗ-6520 рестайлинг самосвал</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-5-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-7-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-restayling-653274-8-1-(1).jpg</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4840187</t>
+          <t>4256288</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>4150</v>
+        <v>8300</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3352,25 +3352,25 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>654956</v>
+        <v>326092</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>KAMAZ-65225 (рестайлинг)</t>
+          <t>КАМАЗ-54901 с п/п НЕФАЗ-93341 белый</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/902-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/901-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/904.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/903-(2).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/905.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/907.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/906.jpg</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4849168</t>
+          <t>4381093</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3300</v>
+        <v>6800</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3415,34 +3415,34 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>198946</v>
+        <v>326092</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>КРАЗ-257Б1 контейнер</t>
+          <t>КАМАЗ-54901 с полуприцепом НЕФАЗ-93341</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-10.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-54901-c-p-p-nefaz-93341-114511-11.jpg</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4910920</t>
+          <t>4386018</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3800</v>
+        <v>5900</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>КрАЗ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3455,11 +3455,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>SSM4017</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3467,7 +3463,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3482,34 +3478,34 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>633016</v>
+        <v>717502</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>КАМАЗ-5511 самосвал темно-зеленый</t>
+          <t>AVD Автокран КС-3577 (500А)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/avtokran-ks-3577-500a-666984.jpg</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>4912801</t>
+          <t>4636941</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6200</v>
+        <v>3700</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>МАЗ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3518,7 +3514,11 @@
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>1707AVD</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Набор новый, запечатанный. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3541,34 +3541,34 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>486148</v>
+        <v>696912</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>АК-75В (130)</t>
+          <t>Икарус 222 светло зеленый</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-2-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-7-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-8-3.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-222-666019-5.jpg</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>4986574</t>
+          <t>4775954</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>6250</v>
+        <v>10250</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ModelPro</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3578,14 +3578,10 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>SSM1549</t>
-        </is>
-      </c>
+          <t>Смола</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3593,7 +3589,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3608,34 +3604,34 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>472677</v>
+        <v>559032</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>КАвЗ-651 рапсодия</t>
+          <t>КО-415А (53213)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/5-18.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/2-23.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/4-19.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/3-20.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/1-30.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ko-415a-53213-117583-8.jpg</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5014580</t>
+          <t>4840187</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3250</v>
+        <v>4150</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>КАвЗ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3656,7 +3652,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3671,34 +3667,34 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>707012</v>
+        <v>654956</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>КММ-2 (51)</t>
+          <t>KAMAZ-65225 (рестайлинг)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65225-restayling-655294.jpg</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>5048762</t>
+          <t>4849168</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>6200</v>
+        <v>3300</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3711,11 +3707,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Бачки</t>
-        </is>
-      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3738,34 +3730,34 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>477641</v>
+        <v>198946</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ikarus-280.64 оранжевый</t>
+          <t>КРАЗ-257Б1 контейнер</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kraz-257b1-konteyner-38206-10.jpg</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5054284</t>
+          <t>4910920</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>6800</v>
+        <v>3800</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>КрАЗ</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3778,7 +3770,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>SSM4017</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3786,7 +3782,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3801,25 +3797,25 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>588726</v>
+        <v>633016</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>КАМАЗ-6522 рестайлинг желтый</t>
+          <t>КАМАЗ-5511 самосвал темно-зеленый</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-5511-114063-6.jpg</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>5085617</t>
+          <t>4912801</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>6800</v>
+        <v>6200</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3828,7 +3824,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3836,11 +3832,7 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
@@ -3849,7 +3841,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3864,25 +3856,25 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>459312</v>
+        <v>486148</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ЗИЛ-4333 KО-829А поливалка</t>
+          <t>АК-75В (130)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-10.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-2-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-4-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-7-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75v-130-116153-8-3.jpg</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>5294623</t>
+          <t>4986574</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>5250</v>
+        <v>6250</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3904,7 +3896,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>SSM1549</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -3927,34 +3923,34 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>342833</v>
+        <v>472677</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Автобус ЛиАЗ-677М красный СОВА</t>
+          <t>КАвЗ-651 рапсодия</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-5-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/5-18.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/2-23.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/4-19.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/3-20.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/1-30.jpg</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5698674</t>
+          <t>5014580</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3300</v>
+        <v>3250</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>КАвЗ</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3990,29 +3986,29 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>470904</v>
+        <v>707012</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tatra-815S3 самосвал оранжевый/синий</t>
+          <t>КММ-2 (51)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kmm-2-51-118047-9.jpg</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>5711242</t>
+          <t>5048762</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>6250</v>
+        <v>6200</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4032,7 +4028,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>SSM1538</t>
+          <t>Бачки</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4042,7 +4038,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4057,25 +4053,25 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>488484</v>
+        <v>477641</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Бокс 32 см (32х9х9) DEMPRICE с винтами</t>
+          <t>Ikarus-280.64 оранжевый</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101849.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-64-115242-6.jpg</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6122001</t>
+          <t>5054284</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1250</v>
+        <v>6800</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -4084,7 +4080,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4094,7 +4090,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Пластмасса</t>
+          <t>Металл/пластмасса</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4105,7 +4101,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Бокс новый.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4120,25 +4116,25 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>487535</v>
+        <v>588726</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KAMAЗ-43253 Рестайлинг</t>
+          <t>КАМАЗ-6522 рестайлинг желтый</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-653272-7.jpg</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>6249403</t>
+          <t>5085617</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>5650</v>
+        <v>6800</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4183,34 +4179,34 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>640208</v>
+        <v>459312</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>КАМАЗ-43118 рестайлинг</t>
+          <t>ЗИЛ-4333 KО-829А поливалка</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ssm1519-k-yu-829-r-4333-10.jpg</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>639065</t>
+          <t>5294623</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>4900</v>
+        <v>5250</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4231,7 +4227,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4246,34 +4242,34 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>473852</v>
+        <v>342833</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Икарус 250.70 Чили ИНТУРИСТ DEMPRICE</t>
+          <t>Автобус ЛиАЗ-677М красный СОВА</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184241_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184254_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184312_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184333_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184354_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184415.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184450_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184950_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184840_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_185157_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mkrb-5-(1).jpg</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>6455073</t>
+          <t>5698674</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>15300</v>
+        <v>3300</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>ЛиАЗ</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4294,7 +4290,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4309,34 +4305,34 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>342832</v>
+        <v>470904</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Автобус ЛиАЗ-677М бело-синий СОВА</t>
+          <t>Tatra-815S3 самосвал оранжевый/синий</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-6-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s3-samosval-114503-8.jpg</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>6498567</t>
+          <t>5711242</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3250</v>
+        <v>6250</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4349,7 +4345,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>SSM1538</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4372,34 +4372,34 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>334587</v>
+        <v>488484</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Прицеп МАЗ-8926</t>
+          <t>Бокс 32 см (32х9х9) DEMPRICE с винтами</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20240710_101849.jpg</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>6762234</t>
+          <t>6122001</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2250</v>
+        <v>1250</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>МАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Металл/пластмасса</t>
+          <t>Пластмасса</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Бокс новый.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4435,34 +4435,34 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>474035</v>
+        <v>487535</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Икарус 250.70 клубничный ИНТУРИСТ</t>
+          <t>KAMAЗ-43253 Рестайлинг</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173347.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173351_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173403.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173413.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173417_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173528.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173603_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173612.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-12.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43253-restayling-117301-8.jpg</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6773621</t>
+          <t>6249403</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>15300</v>
+        <v>5650</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4498,34 +4498,34 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>519214</v>
+        <v>460541</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KAMAZ-6520-21010-53 самосвал</t>
+          <t>Автобус Икарус-260 желтый</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-113837-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-113837.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-113837-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-113837-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-113837-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-260-113837-6.jpg</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>7206133</t>
+          <t>6389774</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>4250</v>
+        <v>4200</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4561,34 +4561,34 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>205299</v>
+        <v>640208</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>КрАЗ-6322 БРО-200</t>
+          <t>КАМАЗ-43118 рестайлинг</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-11.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-2-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-restayling-655297-8.jpg</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>7250974</t>
+          <t>639065</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2050</v>
+        <v>4900</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>КрАЗ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Наш Автопром</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4601,11 +4601,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Н947</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4628,21 +4624,21 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>507465</v>
+        <v>473852</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Автобус Икарус-250.58 Совтрансавто</t>
+          <t>Икарус 250.70 Чили ИНТУРИСТ DEMPRICE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060555.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060600_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060606_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060611.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060615.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060619_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060627_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060740_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060800.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351-(2).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184241_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184254_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184312_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184333_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184354_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184415.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184450_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184950_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_184840_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230525_185157_1.jpg</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>7322725</t>
+          <t>6455073</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -4676,7 +4672,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -4691,34 +4687,34 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>564883</v>
+        <v>342832</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KAMAZ-65952 самосвал</t>
+          <t>Автобус ЛиАЗ-677М бело-синий СОВА</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-4-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-1-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-3-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-5-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/677mbsin-6-(1).jpg</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>7408909</t>
+          <t>6498567</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>4200</v>
+        <v>3250</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>ЛиАЗ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4739,7 +4735,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -4754,34 +4750,34 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>499198</v>
+        <v>334587</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Икарус-280 белый с красной полосой</t>
+          <t>Прицеп МАЗ-8926</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/pricep-maz-8926-89802-7.jpg</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>7438713</t>
+          <t>6762234</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>6250</v>
+        <v>2250</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>МАЗ</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4802,7 +4798,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -4817,34 +4813,34 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>519215</v>
+        <v>474035</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KAMAZ-65207-87 (S5) бортовой</t>
+          <t>Икарус 250.70 клубничный ИНТУРИСТ</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173347.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173351_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173403.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173413.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173417_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173528.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173603_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230514_173612.jpg</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>7494811</t>
+          <t>6773621</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>4900</v>
+        <v>15300</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4865,7 +4861,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -4880,34 +4876,34 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>177912</v>
+        <v>519214</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Полуприцеп МАЗ-5215 зелёный</t>
+          <t>KAMAZ-6520-21010-53 самосвал</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-4-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6520-21010-53-115229-9.jpg</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>7640294</t>
+          <t>7206133</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1750</v>
+        <v>4250</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>МАЗ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4920,11 +4916,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>SSM7011</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4947,34 +4939,34 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>474047</v>
+        <v>205299</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Автобус Икарус 280.33 г. Орёл</t>
+          <t>КрАЗ-6322 БРО-200</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141310.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141318_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141322.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141330_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141335_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141340.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141352_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141456.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141651.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141816.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-01.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-03.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-02.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-04.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-05.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-09.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-08.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-06.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-07.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/n947-ta-r-ch-6322-s-a-yu-200-11.jpg</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>7680062</t>
+          <t>7250974</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>15300</v>
+        <v>2050</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>КрАЗ</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Наш Автопром</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4982,8 +4974,16 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Н947</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5006,34 +5006,34 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>477068</v>
+        <v>507465</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>КамАЗ-65802-87 (S5)</t>
+          <t>Автобус Икарус-250.58 Совтрансавто</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-9-1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060555.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060600_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060606_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060611.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060615.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060619_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060627_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060740_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_060800.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20241112_055351-(2).jpg</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>7722142</t>
+          <t>7322725</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>7150</v>
+        <v>15300</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5046,11 +5046,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>SSM1546</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5073,34 +5069,34 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>180403</v>
+        <v>564883</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>АК-75 (на шасси ЗИЛ-164), голубой/жёлтый</t>
+          <t>KAMAZ-65952 самосвал</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-14.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-2-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65952-114064-7.jpg</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>7814270</t>
+          <t>7408909</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>5700</v>
+        <v>4200</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5113,11 +5109,7 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>SSM1129</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5140,34 +5132,34 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>657404</v>
+        <v>499198</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>КамАЗ-6522 оранжевый</t>
+          <t>Икарус-280 белый с красной полосой</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ikarus-280-33-115243-6.jpg</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>785738</t>
+          <t>7438713</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>4250</v>
+        <v>6250</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Советский Автобус</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5188,7 +5180,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5203,34 +5195,34 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>441961</v>
+        <v>519215</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Мусоровоз КО-413 (53) SSM</t>
+          <t>KAMAZ-65207-87 (S5) бортовой</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/d5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65207-87-s5-115232-8.jpg</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>7902021</t>
+          <t>7494811</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>4650</v>
+        <v>4900</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5251,7 +5243,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5266,34 +5258,34 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>509636</v>
+        <v>177912</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>МКЗ-10 (4333)</t>
+          <t>Полуприцеп МАЗ-5215 зелёный</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/polupricep-maz-5215-zelyonyy-20400-4-(1).jpg</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>8192241</t>
+          <t>7640294</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2250</v>
+        <v>1750</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>МАЗ</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5306,7 +5298,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>SSM7011</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5314,7 +5310,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5329,34 +5325,34 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>714392</v>
+        <v>474047</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ДЭ-210 (ЗИЛ-131)</t>
+          <t>Автобус Икарус 280.33 г. Орёл</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/legendarnye-gruzoviki-sssr-104-zil-mmz-4510-118824-11.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141310.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141318_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141322.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141330_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141335_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141340.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141352_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141359_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141456.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141651.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231124_141816.jpg</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>8329937</t>
+          <t>7680062</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>5700</v>
+        <v>15300</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5364,16 +5360,8 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>SSM1633</t>
-        </is>
-      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5381,7 +5369,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Модель новая. Журнал и открытка в комплекте Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5396,34 +5384,34 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>495095</v>
+        <v>477068</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PETERBILT 350</t>
+          <t>КамАЗ-65802-87 (S5)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250313_142201.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-3-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115150-9-1.jpg</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>8339384</t>
+          <t>7722142</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>4150</v>
+        <v>7150</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Peterbilt</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>IXO грузовики (серии TRU)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5431,8 +5419,16 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>SSM1546</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5440,7 +5436,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая!Оплата на карту сбербанка или при встрече в Химках.Почта по России от 400 рублей, после 100% оплаты.</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5455,34 +5451,34 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>479880</v>
+        <v>180403</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AVD троллейбус SKODA-9TR</t>
+          <t>АК-75 (на шасси ЗИЛ-164), голубой/жёлтый</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115268.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-14.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/ak-75-na-shassi-zil-164-goluboyzhyoltyy-24010-1.jpg</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>8743606</t>
+          <t>7814270</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2500</v>
+        <v>5700</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Škoda</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>AVD Models</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5497,7 +5493,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>4021AVD</t>
+          <t>SSM1129</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5522,34 +5518,34 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>630206</v>
+        <v>657404</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Norba KI-12 (5334) мусоровоз</t>
+          <t>КамАЗ-6522 оранжевый</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-8.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-6522-restayling-655358-8.jpg</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>8843536</t>
+          <t>785738</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>6250</v>
+        <v>4250</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>МАЗ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5585,34 +5581,34 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>472681</v>
+        <v>441961</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Автобус ЛАЗ-695Н бело-красный</t>
+          <t>Мусоровоз КО-413 (53) SSM</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111725.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111705_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111702.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111708_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111711_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111220_1-(1).jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/d5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/d9.jpg</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>8879921</t>
+          <t>7902021</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>5800</v>
+        <v>4650</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>ЛАЗ</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5633,7 +5629,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -5648,34 +5644,34 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>472729</v>
+        <v>509636</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tatra 815 V26 бортовая с тентом</t>
+          <t>МКЗ-10 (4333)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0021.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0023.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0022.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0024.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0025.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0026.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/mkz-10-4333-112724-7.jpg</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>8914544</t>
+          <t>8192241</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>5750</v>
+        <v>2250</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5711,29 +5707,29 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>469263</v>
+        <v>714392</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tatra-815S1 самосвал красный</t>
+          <t>ДЭ-210 (ЗИЛ-131)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-9.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/legendarnye-gruzoviki-sssr-104-zil-mmz-4510-118824-11.jpg</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>9007302</t>
+          <t>8329937</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>5750</v>
+        <v>5700</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5753,7 +5749,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>SSM1537</t>
+          <t>SSM1633</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5763,7 +5759,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Журнал и открытка в комплекте Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -5778,34 +5774,34 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>491552</v>
+        <v>495095</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Троллейбус Skoda-9TR</t>
+          <t>PETERBILT 350</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250313_142201.jpg</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>9103969</t>
+          <t>8339384</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3050</v>
+        <v>4150</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Škoda</t>
+          <t>Peterbilt</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>IXO грузовики (серии TRU)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5813,11 +5809,7 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
@@ -5841,34 +5833,34 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>516931</v>
+        <v>479880</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>КамАЗ-65802-87 (S5) самосвал</t>
+          <t>AVD троллейбус SKODA-9TR</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-9-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-10-1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115268.jpg</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>9158455</t>
+          <t>8743606</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>5250</v>
+        <v>2500</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Škoda</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5881,7 +5873,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>4021AVD</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -5904,34 +5900,34 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>695471</v>
+        <v>630206</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Полуприцеп НАМИ-790</t>
+          <t>Norba KI-12 (5334) мусоровоз</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-2.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/norba-ki-12-5334-656390-8.jpg</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>9199667</t>
+          <t>8843536</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3750</v>
+        <v>6250</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>НАМИ</t>
+          <t>МАЗ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5967,29 +5963,29 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>473509</v>
+        <v>472681</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Автобус Икарус 256.54 Киноварь</t>
+          <t>Автобус ЛАЗ-695Н бело-красный</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191021_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191025_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191029.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191032_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191036.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191048_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191107_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191147_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191207_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111725.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111705_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111702.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111708_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111711_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250108_111220_1-(1).jpg</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>92437</t>
+          <t>8879921</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>9300</v>
+        <v>5800</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>ЛАЗ</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6015,7 +6011,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6030,36 +6026,44 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>178808</v>
+        <v>472729</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Бокс SSM (26,3x10,8x10,9 см)</t>
+          <t>Tatra 815 V26 бортовая с тентом</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/boks-ssm-263x108x109-sm-22425.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0021.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0023.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0022.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0024.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0025.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img-20240308-wa0026.jpg</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>9263175</t>
+          <t>8914544</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1050</v>
-      </c>
-      <c r="G89" t="inlineStr"/>
+        <v>5750</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Start Scale Models (SSM)</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Пластмасса</t>
+          <t>Металл/пластмасса</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -6070,7 +6074,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Бокс новый!Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6085,29 +6089,29 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>675784</v>
+        <v>469263</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ТВГ-15М (51А)</t>
+          <t>Tatra-815S1 самосвал красный</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-4.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tatra-815s1-114502-9.jpg</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>9268253</t>
+          <t>9007302</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>5800</v>
+        <v>5750</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Горький</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6125,7 +6129,11 @@
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>SSM1537</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -6133,7 +6141,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6148,34 +6156,34 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>557769</v>
+        <v>491552</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Троллейбус ЗИУ-5 синий, маршрут №41 Москва</t>
+          <t>Троллейбус Skoda-9TR</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112326_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112331.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112334_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112337_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112350.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-9tr-115234-6.jpg</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>9523751</t>
+          <t>9103969</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>7200</v>
+        <v>3050</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>ЗиУ</t>
+          <t>Škoda</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6196,7 +6204,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6211,34 +6219,34 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>156421</v>
+        <v>516931</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Автобус ЗиЛ-158А экскурсионный</t>
+          <t>КамАЗ-65802-87 (S5) самосвал</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-5.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-9-(1).jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-65802-87-s5-115228-10-1.jpg</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>9533455</t>
+          <t>9158455</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1850</v>
+        <v>5250</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Советский Автобус</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6274,34 +6282,34 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>666531</v>
+        <v>695471</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>КАМАЗ-43118 бортовой</t>
+          <t>Полуприцеп НАМИ-790</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-7.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/nami-790-666007-2.jpg</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>9578983</t>
+          <t>9199667</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3800</v>
+        <v>3750</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>НАМИ</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>ПАО КАМАЗ</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6337,34 +6345,34 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>637799</v>
+        <v>473509</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AVD Пожарная автолестница АЛМ-30 (157)</t>
+          <t>Автобус Икарус 256.54 Киноварь</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pozharnaya-avtolestnica-alm-30-157-655277.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191021_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191025_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191029.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191032_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191036.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191048_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191107_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191147_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20231118_191207_1.jpg</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>9675080</t>
+          <t>92437</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3055</v>
+        <v>9300</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>AVD Models</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6385,7 +6393,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Набор новый, в пленке. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -6400,51 +6408,39 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>221706</v>
+        <v>178808</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ГЗСА-3723 (53А) Автолавка</t>
+          <t>Бокс SSM (26,3x10,8x10,9 см)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/gorkiy-3307-dvigatel-zmz-513-derev-bort-haki-seryy-23504-6.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/boks-ssm-263x108x109-sm-22425.jpg</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>9798081</t>
+          <t>9263175</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2800</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Горький</t>
-        </is>
-      </c>
+        <v>1050</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>Start Scale Models (SSM)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>SSM1340</t>
-        </is>
-      </c>
+          <t>Пластмасса</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
           <t>Новый</t>
@@ -6452,7 +6448,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+          <t>Бокс новый!Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -6467,34 +6463,34 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>473810</v>
+        <v>675784</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Икарус-250.70 Интурист земляничный</t>
+          <t>ТВГ-15М (51А)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162825_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162830_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162835_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162845.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163006_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163018_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163042.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163057_1.jpg</t>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-9.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-7.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-6.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/tvg-15m-51a-658479-4.jpg</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>9840829</t>
+          <t>9268253</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>12300</v>
+        <v>5800</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ikarus</t>
+          <t>Горький</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>DEMPRICE</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6515,15 +6511,464 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="n">
+        <v>557769</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Троллейбус ЗИУ-5 синий, маршрут №41 Москва</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112326_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112331.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112334_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112337_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112350.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20250107_112411_1.jpg</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>9523751</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ЗиУ</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Модель новая. Штанги и зеркала в пакетике.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка Почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="n">
+        <v>156421</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Автобус ЗиЛ-158А экскурсионный</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-10.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/zil-158a-ekskursionnyy-13076-5.jpg</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>9533455</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Советский Автобус</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="n">
+        <v>666531</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>КАМАЗ-43118 бортовой</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-8.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-2.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-3.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-4.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-5.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/kamaz-43118-655365-7.jpg</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>9578983</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>3800</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ПАО КАМАЗ</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="n">
+        <v>280993</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Троллейбус Skoda-14TR, Eberswalde</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-14tr-eberswalde-80359-15.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-14tr-eberswalde-80359-17.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-14tr-eberswalde-80359.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-14tr-eberswalde-80359-16.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-14tr-eberswalde-80359-18.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-14tr-eberswalde-80359-19.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-14tr-eberswalde-80359-20.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-14tr-eberswalde-80359-1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/skoda-14tr-eberswalde-80359-3.jpg</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>9635062</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Škoda</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Premium Classixxs</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>PCL47066</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки.Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="n">
+        <v>637799</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>AVD Пожарная автолестница АЛМ-30 (157)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/pozharnaya-avtolestnica-alm-30-157-655277.jpg</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>9675080</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>3055</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>AVD Models</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Набор новый, в пленке. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="n">
+        <v>221706</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ГЗСА-3723 (53А) Автолавка</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/gorkiy-3307-dvigatel-zmz-513-derev-bort-haki-seryy-23504-6.jpg</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>9798081</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Горький</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>SSM1340</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Модель новая. Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="n">
+        <v>473810</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Икарус-250.70 Интурист земляничный</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162810.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162819.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162825_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162830_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162835_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_162845.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163006_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163018_1.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163042.jpg;https://scalebay.ru/static/old/user/s/o/sova_7701/img_20230516_163057_1.jpg</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>9840829</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>12300</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>DEMPRICE</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
           <t>Модель новая.Самовывоз возможен только в г. Химки (Набережный проезд 3).Отправка почтой России или СДЭК от 500 рублей в зависимости от габаритов, веса и дальности отправки посылки. Выход на связь 3 дня, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>г Химки, кв-л Клязьма</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>г Химки, кв-л Клязьма</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Matched Far" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,27 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +53,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +433,104 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID UNOMAG</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Фото (ссылки)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Лот №</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Единая цена</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Масштаб</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Состояние</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Местоположение</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Наличие</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Matched Far" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matched Far" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matched Far" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,27 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,104 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID UNOMAG</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Название</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Фото (ссылки)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Лот №</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Единая цена</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Марка</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Производитель</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Масштаб</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Материал</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Артикул</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Состояние</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Описание</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Местоположение</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Наличие</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matched Far" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,27 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +53,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +433,104 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID UNOMAG</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Фото (ссылки)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Лот №</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Единая цена</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Масштаб</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Состояние</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Местоположение</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Наличие</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matched Far" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,27 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +53,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +433,104 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID UNOMAG</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Фото (ссылки)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Лот №</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Единая цена</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Марка</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Масштаб</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Артикул</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Состояние</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Описание</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Местоположение</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Наличие</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/matched_far.xlsx
+++ b/matched_far.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matched Far" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,27 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,104 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID UNOMAG</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Название</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Фото (ссылки)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Лот №</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Единая цена</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Марка</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Производитель</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Масштаб</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Материал</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Артикул</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Состояние</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Описание</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Местоположение</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Наличие</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>